--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25524,25 +25524,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.09578118377923987</v>
+        <v>0.09578120863437674</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04522043298929932</v>
+        <v>0.04522044472396376</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.02584024742245676</v>
+        <v>0.0258402541279793</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.06089684975892308</v>
+        <v>0.06089686556160453</v>
       </c>
       <c r="J2" s="1">
-        <v>0.03979398103058341</v>
+        <v>0.03979399135708812</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -25551,10 +25551,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08802910955250284</v>
+        <v>0.08802913239598295</v>
       </c>
       <c r="N2" s="1">
-        <v>0.03876037113368511</v>
+        <v>0.03876038119196892</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -25566,7 +25566,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.07769301058351995</v>
+        <v>0.07769303074479104</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -25575,7 +25575,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.5279848137497902</v>
+        <v>0.5279846912622452</v>
       </c>
     </row>
     <row r="3">
@@ -25808,25 +25808,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.09953401703587546</v>
+        <v>0.09953402737947123</v>
       </c>
       <c r="E6" s="1">
-        <v>0.08972592046664685</v>
+        <v>0.08972592979098316</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02179577015384136</v>
+        <v>0.02179577241886233</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1220563128615113</v>
+        <v>0.1220563255456288</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.07010972732818965</v>
+        <v>0.0701097346140071</v>
       </c>
       <c r="J6" s="1">
-        <v>0.01525703910768895</v>
+        <v>0.01525704069320363</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -25835,10 +25835,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.05230984836921922</v>
+        <v>0.05230985380526955</v>
       </c>
       <c r="N6" s="1">
-        <v>0.03269365523076201</v>
+        <v>0.03269365862829347</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -25850,16 +25850,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.0624812077743452</v>
+        <v>0.06248121426740531</v>
       </c>
       <c r="S6" s="1">
-        <v>0.01525703910768895</v>
+        <v>0.01525704069320363</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.4187794625642309</v>
+        <v>0.4187794021636717</v>
       </c>
     </row>
     <row r="7">
@@ -30267,16 +30267,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.2675326949805025</v>
+        <v>0.2675327644050124</v>
       </c>
       <c r="E2" s="1">
-        <v>0.03876037113368511</v>
+        <v>0.03876038119196892</v>
       </c>
       <c r="F2" s="1">
-        <v>0.1657221201360228</v>
+        <v>0.165722163140774</v>
       </c>
       <c r="G2" s="1">
-        <v>0.5279848137497902</v>
+        <v>0.5279846912622452</v>
       </c>
     </row>
     <row r="3">
@@ -30383,16 +30383,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.4184787869537536</v>
+        <v>0.4184788304421563</v>
       </c>
       <c r="E6" s="1">
-        <v>0.04795069433845096</v>
+        <v>0.0479506993214971</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1147910561435644</v>
+        <v>0.1147910680726749</v>
       </c>
       <c r="G6" s="1">
-        <v>0.4187794625642309</v>
+        <v>0.4187794021636717</v>
       </c>
     </row>
     <row r="7">
@@ -32322,25 +32322,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.1173905918896201</v>
+        <v>0.1173906043171885</v>
       </c>
       <c r="E2" s="1">
-        <v>0.05542271649464968</v>
+        <v>0.0554227223619819</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0316701237112284</v>
+        <v>0.03167012706398967</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.07463592487946155</v>
+        <v>0.07463593278080229</v>
       </c>
       <c r="J2" s="1">
-        <v>0.04877199051529173</v>
+        <v>0.04877199567854408</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -32349,10 +32349,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1078895547762516</v>
+        <v>0.1078895661979916</v>
       </c>
       <c r="N2" s="1">
-        <v>0.04750518556684256</v>
+        <v>0.04750519059598446</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -32364,7 +32364,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.09522150529175999</v>
+        <v>0.09522151537239554</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -32373,7 +32373,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4214924068748951</v>
+        <v>0.4214923456311226</v>
       </c>
     </row>
     <row r="3">
@@ -32606,25 +32606,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920085179377</v>
+        <v>0.1353920136897356</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504602333234</v>
+        <v>0.1220504648954916</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0296478850769207</v>
+        <v>0.02964788620943118</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281564307555</v>
+        <v>0.1660281627728142</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736366409483</v>
+        <v>0.09536736730700356</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075351955384449</v>
+        <v>0.02075352034660183</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -32633,10 +32633,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492418460961</v>
+        <v>0.07115492690263478</v>
       </c>
       <c r="N6" s="1">
-        <v>0.044471827615381</v>
+        <v>0.04447182931414673</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -32648,16 +32648,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060388717261</v>
+        <v>0.08499060713370268</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075351955384449</v>
+        <v>0.02075352034660183</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897312821155</v>
+        <v>0.2093897010818359</v>
       </c>
     </row>
     <row r="7">
@@ -37065,16 +37065,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3278913474902515</v>
+        <v>0.3278913822025065</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04750518556684256</v>
+        <v>0.04750519059598446</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2031110600680116</v>
+        <v>0.2031110815703872</v>
       </c>
       <c r="G2" s="1">
-        <v>0.4214924068748951</v>
+        <v>0.4214923456311226</v>
       </c>
     </row>
     <row r="3">
@@ -37181,16 +37181,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692393934768767</v>
+        <v>0.569239415221078</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0652253471692255</v>
+        <v>0.06522534966074857</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455280717822</v>
+        <v>0.1561455340363375</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897312821155</v>
+        <v>0.2093897010818359</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25374,14 +25374,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
@@ -25398,6 +25398,8 @@
     <col min="19" max="19" width="9" customWidth="1"/>
     <col min="20" max="20" width="9" customWidth="1"/>
     <col min="21" max="21" width="9" customWidth="1"/>
+    <col min="22" max="22" width="9" customWidth="1"/>
+    <col min="23" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25418,90 +25420,100 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">State</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk Budget</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">QQQ</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SPY</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IWM</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EEM</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EFA</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EWY</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">VGK</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AGG</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TIP</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">DBC</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IEF</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TLT</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LQD</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">VNQ</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GLD</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HYG</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SHY</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BIL</t>
         </is>
@@ -25523,59 +25535,67 @@
           <t xml:space="preserve">2026-10</t>
         </is>
       </c>
-      <c r="D2" s="1">
-        <v>0.09578120863437674</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
       </c>
       <c r="E2" s="1">
-        <v>0.04522044472396376</v>
+        <v>0.6890736222267151</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>0.09578123348951362</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0258402541279793</v>
+        <v>0.0452204564586282</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.06089686556160453</v>
+        <v>0.02584026083350184</v>
       </c>
       <c r="J2" s="1">
-        <v>0.03979399135708812</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>0.06089688136428597</v>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>0.03979400168359282</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08802913239598295</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1">
-        <v>0.03876038119196892</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0</v>
+        <v>0.08802915523946306</v>
       </c>
       <c r="P2" s="1">
-        <v>0</v>
+        <v>0.03876039125025273</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.07769303074479104</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
       </c>
       <c r="T2" s="1">
-        <v>0</v>
+        <v>0.07769305090606214</v>
       </c>
       <c r="U2" s="1">
-        <v>0.5279846912622452</v>
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.5279845687747001</v>
       </c>
     </row>
     <row r="3">
@@ -25594,58 +25614,66 @@
           <t xml:space="preserve">2026-09</t>
         </is>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
         <v>0.1300000000000003</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.06000000000000003</v>
       </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.07937500000000003</v>
       </c>
-      <c r="J3" s="1">
+      <c r="L3" s="1">
         <v>0.04875000000000004</v>
       </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
       <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
         <v>0.09375000000000031</v>
       </c>
-      <c r="N3" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O3" s="1">
-        <v>0</v>
-      </c>
       <c r="P3" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
         <v>0.0225</v>
       </c>
-      <c r="R3" s="1">
+      <c r="T3" s="1">
         <v>0.10375</v>
       </c>
-      <c r="S3" s="1">
-        <v>0</v>
-      </c>
-      <c r="T3" s="1">
-        <v>0</v>
-      </c>
       <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
         <v>0.315</v>
       </c>
     </row>
@@ -25665,58 +25693,66 @@
           <t xml:space="preserve">2026-08</t>
         </is>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>0.06562500000000003</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.04875000000000004</v>
       </c>
       <c r="H4" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="I4" s="1">
+        <v>0.04875000000000004</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
       <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
         <v>0.16</v>
       </c>
-      <c r="N4" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0</v>
-      </c>
       <c r="P4" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R4" s="1">
+      <c r="T4" s="1">
         <v>0.08125</v>
       </c>
-      <c r="S4" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T4" s="1">
-        <v>0</v>
-      </c>
       <c r="U4" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -25736,58 +25772,66 @@
           <t xml:space="preserve">2026-07</t>
         </is>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
+      </c>
+      <c r="E5" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.09707499999999986</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>0.08779374999999985</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.02062500000000002</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.1328249999999998</v>
       </c>
       <c r="H5" s="1">
         <v>0.02062500000000002</v>
       </c>
       <c r="I5" s="1">
+        <v>0.1328249999999998</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.02062500000000002</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.05190624999999998</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L5" s="1">
         <v>0.01443750000000002</v>
       </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
       <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
         <v>0.01732500000000001</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>0.0309375</v>
       </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
       <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
         <v>0.01443750000000002</v>
       </c>
-      <c r="R5" s="1">
+      <c r="T5" s="1">
         <v>0.0446875</v>
       </c>
-      <c r="S5" s="1">
+      <c r="U5" s="1">
         <v>0.01732500000000001</v>
       </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-      <c r="U5" s="1">
+      <c r="V5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
         <v>0.45</v>
       </c>
     </row>
@@ -25807,59 +25851,67 @@
           <t xml:space="preserve">2026-06</t>
         </is>
       </c>
-      <c r="D6" s="1">
-        <v>0.09953402737947123</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
       </c>
       <c r="E6" s="1">
-        <v>0.08972592979098316</v>
+        <v>0.581220578710214</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02179577241886233</v>
+        <v>0.09953402410412417</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1220563255456288</v>
+        <v>0.08972592683838929</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>0.02179577170163305</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0701097346140071</v>
+        <v>0.1220563215291448</v>
       </c>
       <c r="J6" s="1">
-        <v>0.01525704069320363</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>0.07010973230691958</v>
       </c>
       <c r="L6" s="1">
-        <v>0</v>
+        <v>0.01525704019114314</v>
       </c>
       <c r="M6" s="1">
-        <v>0.05230985380526955</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>0.03269365862829347</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>0.05230985208391927</v>
       </c>
       <c r="P6" s="1">
-        <v>0</v>
+        <v>0.03269365755244954</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.06248121426740531</v>
+        <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>0.01525704069320363</v>
+        <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0</v>
+        <v>0.06248121221134803</v>
       </c>
       <c r="U6" s="1">
-        <v>0.4187794021636717</v>
+        <v>0.01525704019114314</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.418779421289786</v>
       </c>
     </row>
     <row r="7">
@@ -25878,58 +25930,66 @@
           <t xml:space="preserve">2026-05</t>
         </is>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>0.129375</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>0.2099999999999997</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
         <v>0.115</v>
       </c>
-      <c r="N7" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
       <c r="P7" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T7" s="1">
         <v>0.1075</v>
       </c>
-      <c r="S7" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
       <c r="U7" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25949,58 +26009,66 @@
           <t xml:space="preserve">2026-04</t>
         </is>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
         <v>0.05650000000000001</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>0.07087500000000001</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>0.07499999999999997</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>0.1258749999999997</v>
       </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
       <c r="L8" s="1">
         <v>0</v>
       </c>
       <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
         <v>0.1402499999999997</v>
       </c>
-      <c r="N8" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
       <c r="P8" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
       </c>
       <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="S8" s="1">
+      <c r="U8" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="T8" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="V8" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="W8" s="1">
         <v>0.1424999999999997</v>
       </c>
     </row>
@@ -26020,58 +26088,66 @@
           <t xml:space="preserve">2026-03</t>
         </is>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>0.1075</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>0.09062500000000004</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.2349999999999997</v>
       </c>
       <c r="H9" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="I9" s="1">
+        <v>0.2349999999999997</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="K9" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J9" s="1">
+      <c r="L9" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
       <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="N9" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
       <c r="P9" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T9" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S9" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
       <c r="U9" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26091,58 +26167,66 @@
           <t xml:space="preserve">2026-02</t>
         </is>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>0.1168749999999997</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.2349999999999997</v>
       </c>
       <c r="H10" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="I10" s="1">
+        <v>0.2349999999999997</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="K10" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J10" s="1">
+      <c r="L10" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
       <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="N10" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
       <c r="P10" s="1">
-        <v>0.02625000000000003</v>
+        <v>0.05625</v>
       </c>
       <c r="Q10" s="1">
         <v>0</v>
       </c>
       <c r="R10" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S10" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
       <c r="U10" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26162,58 +26246,66 @@
           <t xml:space="preserve">2026-01</t>
         </is>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
         <v>0.2349999999999997</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J11" s="1">
+      <c r="L11" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
       <c r="M11" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P11" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
       </c>
       <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S11" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
       <c r="U11" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26233,58 +26325,66 @@
           <t xml:space="preserve">2025-12</t>
         </is>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
         <v>0.2349999999999997</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J12" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
       <c r="L12" s="1">
         <v>0.02625000000000003</v>
       </c>
       <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O12" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="N12" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
       <c r="P12" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q12" s="1">
         <v>0</v>
       </c>
       <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
       <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26304,58 +26404,66 @@
           <t xml:space="preserve">2025-11</t>
         </is>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>0.2349999999999997</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J13" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
       <c r="L13" s="1">
         <v>0.02625000000000003</v>
       </c>
       <c r="M13" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O13" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P13" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q13" s="1">
         <v>0</v>
       </c>
       <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S13" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
       <c r="U13" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26375,58 +26483,66 @@
           <t xml:space="preserve">2025-10</t>
         </is>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>0.2349999999999997</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J14" s="1">
+      <c r="L14" s="1">
         <v>0.05775000000000004</v>
       </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0.05625</v>
-      </c>
       <c r="O14" s="1">
         <v>0</v>
       </c>
       <c r="P14" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q14" s="1">
         <v>0</v>
       </c>
       <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
       <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26446,58 +26562,66 @@
           <t xml:space="preserve">2025-09</t>
         </is>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>0.09062500000000004</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.23625</v>
       </c>
       <c r="H15" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="I15" s="1">
+        <v>0.23625</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J15" s="1">
+      <c r="L15" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M15" s="1">
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q15" s="1">
         <v>0</v>
       </c>
       <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
       <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26517,58 +26641,66 @@
           <t xml:space="preserve">2025-08</t>
         </is>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>0.1281249999999997</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H16" s="1">
+      <c r="J16" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>0.120625</v>
       </c>
-      <c r="J16" s="1">
+      <c r="L16" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q16" s="1">
         <v>0</v>
       </c>
       <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
       <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26588,58 +26720,66 @@
           <t xml:space="preserve">2025-07</t>
         </is>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>0.1281249999999997</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>0.025</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H17" s="1">
+      <c r="J17" s="1">
         <v>0.1725000000000003</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J17" s="1">
+      <c r="L17" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M17" s="1">
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O17" s="1">
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>0.02625000000000003</v>
+        <v>0.05625</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
       </c>
       <c r="R17" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
       <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26659,58 +26799,66 @@
           <t xml:space="preserve">2025-06</t>
         </is>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>0.101875</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>0.025</v>
       </c>
-      <c r="G18" s="1">
+      <c r="I18" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H18" s="1">
+      <c r="J18" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J18" s="1">
+      <c r="L18" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M18" s="1">
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q18" s="1">
         <v>0</v>
       </c>
       <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S18" s="1">
+      <c r="U18" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
+      <c r="V18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
         <v>0.135</v>
       </c>
     </row>
@@ -26730,58 +26878,66 @@
           <t xml:space="preserve">2025-05</t>
         </is>
       </c>
-      <c r="D19" s="1">
-        <v>0.025</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
       </c>
       <c r="E19" s="1">
-        <v>0.064375</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
         <v>0.025</v>
       </c>
       <c r="G19" s="1">
+        <v>0.064375</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="I19" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H19" s="1">
+      <c r="J19" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>0.03187500000000003</v>
       </c>
-      <c r="J19" s="1">
+      <c r="L19" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K19" s="1">
+      <c r="M19" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="L19" s="1">
+      <c r="N19" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
         <v>0.1387500000000003</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0.05249999999999997</v>
       </c>
       <c r="Q19" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="R19" s="1">
+        <v>0.05249999999999997</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="T19" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S19" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0.05625</v>
-      </c>
       <c r="U19" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="W19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26801,58 +26957,66 @@
           <t xml:space="preserve">2025-04</t>
         </is>
       </c>
-      <c r="D20" s="1">
-        <v>0.025</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
       </c>
       <c r="E20" s="1">
-        <v>0.064375</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>0.025</v>
       </c>
       <c r="G20" s="1">
+        <v>0.064375</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="I20" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I20" s="1">
+      <c r="K20" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J20" s="1">
+      <c r="L20" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="M20" s="1">
+      <c r="O20" s="1">
         <v>0.135</v>
       </c>
-      <c r="N20" s="1">
+      <c r="P20" s="1">
         <v>0.1387500000000003</v>
       </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
       <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="R20" s="1">
+      <c r="T20" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S20" s="1">
+      <c r="U20" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T20" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="U20" s="1">
+      <c r="V20" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="W20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26872,58 +27036,66 @@
           <t xml:space="preserve">2025-03</t>
         </is>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>0.1281249999999997</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>0.025</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J21" s="1">
+      <c r="L21" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O21" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="N21" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
       <c r="P21" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="R21" s="1">
+      <c r="T21" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S21" s="1">
+      <c r="U21" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26943,58 +27115,66 @@
           <t xml:space="preserve">2025-02</t>
         </is>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>0.07499999999999997</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J22" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="N22" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
       <c r="P22" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q22" s="1">
         <v>0</v>
       </c>
       <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S22" s="1">
+      <c r="U22" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27014,58 +27194,66 @@
           <t xml:space="preserve">2025-01</t>
         </is>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
         <v>0.1390000000000003</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>0.1221250000000003</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>0.025</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="N23" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
       <c r="P23" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q23" s="1">
         <v>0</v>
       </c>
       <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
         <v>0.1390000000000003</v>
       </c>
-      <c r="S23" s="1">
+      <c r="U23" s="1">
         <v>0.05775000000000004</v>
       </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
         <v>0.4124999999999997</v>
       </c>
     </row>
@@ -27085,58 +27273,66 @@
           <t xml:space="preserve">2024-12</t>
         </is>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>0.04875000000000004</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
       <c r="N24" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
       </c>
       <c r="P24" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="S24" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="R24" s="1">
+      <c r="T24" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="S24" s="1">
+      <c r="U24" s="1">
         <v>0.05775000000000004</v>
       </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
+      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
         <v>0.07650000000000001</v>
       </c>
     </row>
@@ -27156,30 +27352,32 @@
           <t xml:space="preserve">2024-11</t>
         </is>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>0.10125</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
       <c r="L25" s="1">
         <v>0</v>
       </c>
@@ -27187,27 +27385,33 @@
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
       </c>
       <c r="P25" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="S25" s="1">
         <v>0.115</v>
       </c>
-      <c r="R25" s="1">
+      <c r="T25" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S25" s="1">
+      <c r="U25" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -27227,58 +27431,66 @@
           <t xml:space="preserve">2024-10</t>
         </is>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
+      </c>
+      <c r="E26" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="F26" s="1">
         <v>0.1684375</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>0.08490625</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>0.03437500000000002</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>0.05568750000000001</v>
       </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
         <v>0.003093750000000001</v>
       </c>
-      <c r="J26" s="1">
+      <c r="L26" s="1">
         <v>0.01443750000000002</v>
       </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
       <c r="M26" s="1">
         <v>0</v>
       </c>
       <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
         <v>0.0309375</v>
       </c>
-      <c r="O26" s="1">
+      <c r="Q26" s="1">
         <v>0.01443750000000002</v>
       </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1">
         <v>0.04950000000000001</v>
       </c>
-      <c r="R26" s="1">
+      <c r="T26" s="1">
         <v>0.09418750000000002</v>
       </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
       <c r="U26" s="1">
+        <v>0</v>
+      </c>
+      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="W26" s="1">
         <v>0.45</v>
       </c>
     </row>
@@ -27298,58 +27510,66 @@
           <t xml:space="preserve">2024-09</t>
         </is>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>0.1281249999999997</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="H27" s="1">
+      <c r="J27" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J27" s="1">
+      <c r="L27" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R27" s="1">
+      <c r="T27" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S27" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
       <c r="U27" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27369,58 +27589,66 @@
           <t xml:space="preserve">2024-08</t>
         </is>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="H28" s="1">
+      <c r="J28" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J28" s="1">
+      <c r="L28" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
       <c r="M28" s="1">
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
       </c>
       <c r="P28" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="R28" s="1">
+      <c r="T28" s="1">
         <v>0.17125</v>
       </c>
-      <c r="S28" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T28" s="1">
-        <v>0</v>
-      </c>
       <c r="U28" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V28" s="1">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27440,58 +27668,66 @@
           <t xml:space="preserve">2024-07</t>
         </is>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
         <v>0.3114999999999998</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F29" s="1">
+      <c r="H29" s="1">
         <v>0.025</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>0.1064999999999997</v>
       </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>0.03187500000000003</v>
       </c>
-      <c r="J29" s="1">
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
       <c r="L29" s="1">
         <v>0</v>
       </c>
       <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
         <v>0.09524999999999971</v>
       </c>
-      <c r="N29" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
       <c r="P29" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q29" s="1">
         <v>0</v>
       </c>
       <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
-      <c r="T29" s="1">
-        <v>0</v>
-      </c>
       <c r="U29" s="1">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1">
+        <v>0</v>
+      </c>
+      <c r="W29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27511,58 +27747,66 @@
           <t xml:space="preserve">2024-06</t>
         </is>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
         <v>0.3114999999999998</v>
       </c>
-      <c r="E30" s="1">
+      <c r="G30" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F30" s="1">
+      <c r="H30" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G30" s="1">
+      <c r="I30" s="1">
         <v>0.1064999999999997</v>
       </c>
-      <c r="H30" s="1">
+      <c r="J30" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I30" s="1">
+      <c r="K30" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J30" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
       <c r="L30" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="N30" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
       <c r="P30" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1">
         <v>0.025</v>
       </c>
-      <c r="R30" s="1">
+      <c r="T30" s="1">
         <v>0.1514999999999997</v>
       </c>
-      <c r="S30" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T30" s="1">
-        <v>0</v>
-      </c>
       <c r="U30" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27582,58 +27826,66 @@
           <t xml:space="preserve">2024-05</t>
         </is>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
         <v>0.1390000000000003</v>
       </c>
-      <c r="E31" s="1">
+      <c r="G31" s="1">
         <v>0.1221250000000003</v>
       </c>
-      <c r="F31" s="1">
+      <c r="H31" s="1">
         <v>0.025</v>
       </c>
-      <c r="G31" s="1">
+      <c r="I31" s="1">
         <v>0.06900000000000003</v>
       </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>0.03187500000000003</v>
       </c>
-      <c r="J31" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
       <c r="L31" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
         <v>0.07650000000000001</v>
       </c>
-      <c r="N31" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
       <c r="P31" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q31" s="1">
         <v>0</v>
       </c>
       <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
         <v>0.1390000000000003</v>
       </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
       <c r="U31" s="1">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1">
         <v>0.315</v>
       </c>
     </row>
@@ -27653,58 +27905,66 @@
           <t xml:space="preserve">2024-04</t>
         </is>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E32" s="1">
+      <c r="G32" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F32" s="1">
+      <c r="H32" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G32" s="1">
+      <c r="I32" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H32" s="1">
+      <c r="J32" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I32" s="1">
+      <c r="K32" s="1">
         <v>0.09437499999999996</v>
       </c>
-      <c r="J32" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
       <c r="L32" s="1">
         <v>0.02625000000000003</v>
       </c>
       <c r="M32" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O32" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P32" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T32" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S32" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
       <c r="U32" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V32" s="1">
+        <v>0</v>
+      </c>
+      <c r="W32" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27724,30 +27984,32 @@
           <t xml:space="preserve">2024-03</t>
         </is>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E33" s="1">
+      <c r="G33" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F33" s="1">
+      <c r="H33" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G33" s="1">
+      <c r="I33" s="1">
         <v>0.07499999999999997</v>
       </c>
-      <c r="H33" s="1">
+      <c r="J33" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I33" s="1">
+      <c r="K33" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J33" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
       <c r="L33" s="1">
         <v>0.02625000000000003</v>
       </c>
@@ -27755,27 +28017,33 @@
         <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
       </c>
       <c r="P33" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="S33" s="1">
         <v>0.05125000000000003</v>
       </c>
-      <c r="R33" s="1">
+      <c r="T33" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="S33" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
       <c r="U33" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="W33" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -27795,58 +28063,66 @@
           <t xml:space="preserve">2024-02</t>
         </is>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E34" s="1">
+      <c r="G34" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F34" s="1">
+      <c r="H34" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G34" s="1">
+      <c r="I34" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H34" s="1">
+      <c r="J34" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I34" s="1">
+      <c r="K34" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J34" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="L34" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="M34" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="L34" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
       <c r="N34" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
         <v>0.09375000000000031</v>
       </c>
-      <c r="O34" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="P34" s="1">
+      <c r="Q34" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="R34" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
+      <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1">
         <v>0.1199999999999997</v>
       </c>
-      <c r="S34" s="1">
+      <c r="U34" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
+      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
@@ -27866,58 +28142,66 @@
           <t xml:space="preserve">2024-01</t>
         </is>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E35" s="1">
+      <c r="G35" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F35" s="1">
+      <c r="H35" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G35" s="1">
+      <c r="I35" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H35" s="1">
+      <c r="J35" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I35" s="1">
+      <c r="K35" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J35" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
       <c r="L35" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
       </c>
       <c r="N35" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
       </c>
       <c r="P35" s="1">
-        <v>0.02625000000000003</v>
+        <v>0.05625</v>
       </c>
       <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="S35" s="1">
         <v>0.08874999999999997</v>
       </c>
-      <c r="R35" s="1">
+      <c r="T35" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S35" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
       <c r="U35" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V35" s="1">
+        <v>0</v>
+      </c>
+      <c r="W35" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27937,58 +28221,66 @@
           <t xml:space="preserve">2023-12</t>
         </is>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
         <v>0.3114999999999998</v>
       </c>
-      <c r="E36" s="1">
+      <c r="G36" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F36" s="1">
+      <c r="H36" s="1">
         <v>0.025</v>
       </c>
-      <c r="G36" s="1">
+      <c r="I36" s="1">
         <v>0.1064999999999997</v>
       </c>
-      <c r="H36" s="1">
+      <c r="J36" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I36" s="1">
+      <c r="K36" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J36" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
       <c r="L36" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
       </c>
       <c r="N36" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
       </c>
       <c r="P36" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
         <v>0.05125000000000003</v>
       </c>
-      <c r="R36" s="1">
+      <c r="T36" s="1">
         <v>0.1252500000000003</v>
       </c>
-      <c r="S36" s="1">
+      <c r="U36" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
-      <c r="U36" s="1">
+      <c r="V36" s="1">
+        <v>0</v>
+      </c>
+      <c r="W36" s="1">
         <v>0</v>
       </c>
     </row>
@@ -28008,58 +28300,66 @@
           <t xml:space="preserve">2023-11</t>
         </is>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
         <v>0.1075</v>
       </c>
-      <c r="E37" s="1">
+      <c r="G37" s="1">
         <v>0.06562500000000003</v>
       </c>
-      <c r="F37" s="1">
+      <c r="H37" s="1">
         <v>0.025</v>
       </c>
-      <c r="G37" s="1">
+      <c r="I37" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
       <c r="L37" s="1">
         <v>0</v>
       </c>
       <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="N37" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
       <c r="P37" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+      <c r="S37" s="1">
         <v>0.025</v>
       </c>
-      <c r="R37" s="1">
+      <c r="T37" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S37" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
       <c r="U37" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V37" s="1">
+        <v>0</v>
+      </c>
+      <c r="W37" s="1">
         <v>0.4912499999999997</v>
       </c>
     </row>
@@ -28079,58 +28379,66 @@
           <t xml:space="preserve">2023-10</t>
         </is>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="E38" s="1">
+      <c r="G38" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F38" s="1">
+      <c r="H38" s="1">
         <v>0.025</v>
       </c>
-      <c r="G38" s="1">
+      <c r="I38" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J38" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="N38" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
       <c r="P38" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q38" s="1">
         <v>0</v>
       </c>
       <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="S38" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
       <c r="U38" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
         <v>0.4200000000000003</v>
       </c>
     </row>
@@ -28150,58 +28458,66 @@
           <t xml:space="preserve">2023-09</t>
         </is>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="E39" s="1">
+      <c r="G39" s="1">
         <v>0.1168749999999997</v>
       </c>
-      <c r="F39" s="1">
+      <c r="H39" s="1">
         <v>0.025</v>
       </c>
-      <c r="G39" s="1">
+      <c r="I39" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J39" s="1">
+      <c r="L39" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
       <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="N39" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
       <c r="P39" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q39" s="1">
         <v>0</v>
       </c>
       <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S39" s="1">
+      <c r="U39" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
         <v>0.36</v>
       </c>
     </row>
@@ -28221,58 +28537,66 @@
           <t xml:space="preserve">2023-08</t>
         </is>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
         <v>0.1390000000000003</v>
       </c>
-      <c r="E40" s="1">
+      <c r="G40" s="1">
         <v>0.1221250000000003</v>
       </c>
-      <c r="F40" s="1">
+      <c r="H40" s="1">
         <v>0.025</v>
       </c>
-      <c r="G40" s="1">
+      <c r="I40" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
         <v>0.08837500000000004</v>
       </c>
-      <c r="J40" s="1">
+      <c r="L40" s="1">
         <v>0.05775000000000004</v>
       </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
       <c r="M40" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P40" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q40" s="1">
         <v>0</v>
       </c>
       <c r="R40" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="S40" s="1">
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U40" s="1">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1">
         <v>0.3915</v>
       </c>
     </row>
@@ -28292,58 +28616,66 @@
           <t xml:space="preserve">2023-07</t>
         </is>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="E41" s="1">
+      <c r="G41" s="1">
         <v>0.1168749999999997</v>
       </c>
-      <c r="F41" s="1">
+      <c r="H41" s="1">
         <v>0.025</v>
       </c>
-      <c r="G41" s="1">
+      <c r="I41" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
         <v>0.05687500000000003</v>
       </c>
-      <c r="J41" s="1">
+      <c r="L41" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
       <c r="M41" s="1">
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
       </c>
       <c r="P41" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="Q41" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="R41" s="1">
+      <c r="S41" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T41" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="S41" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
       <c r="U41" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
         <v>0.3412500000000003</v>
       </c>
     </row>
@@ -28363,58 +28695,66 @@
           <t xml:space="preserve">2023-06</t>
         </is>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="E42" s="1">
+      <c r="G42" s="1">
         <v>0.1168749999999997</v>
       </c>
-      <c r="F42" s="1">
+      <c r="H42" s="1">
         <v>0.025</v>
       </c>
-      <c r="G42" s="1">
+      <c r="I42" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
         <v>0.05687500000000003</v>
       </c>
-      <c r="J42" s="1">
+      <c r="L42" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
       <c r="M42" s="1">
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
       </c>
       <c r="P42" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
       <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
         <v>0.3862500000000003</v>
       </c>
     </row>
@@ -28434,58 +28774,66 @@
           <t xml:space="preserve">2023-05</t>
         </is>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E43" s="1">
+      <c r="G43" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F43" s="1">
+      <c r="H43" s="1">
         <v>0.025</v>
       </c>
-      <c r="G43" s="1">
+      <c r="I43" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H43" s="1">
+      <c r="J43" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="I43" s="1">
+      <c r="K43" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J43" s="1">
+      <c r="L43" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K43" s="1">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M43" s="1">
         <v>0</v>
       </c>
       <c r="N43" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
         <v>0.09375000000000031</v>
       </c>
-      <c r="O43" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="P43" s="1">
+      <c r="Q43" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="R43" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-      <c r="R43" s="1">
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
-      <c r="T43" s="1">
-        <v>0</v>
-      </c>
       <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -28505,58 +28853,66 @@
           <t xml:space="preserve">2023-04</t>
         </is>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E44" s="1">
+      <c r="G44" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F44" s="1">
+      <c r="H44" s="1">
         <v>0.025</v>
       </c>
-      <c r="G44" s="1">
+      <c r="I44" s="1">
         <v>0.07499999999999997</v>
       </c>
-      <c r="H44" s="1">
+      <c r="J44" s="1">
         <v>0.1975000000000003</v>
       </c>
-      <c r="I44" s="1">
+      <c r="K44" s="1">
         <v>0.06937499999999996</v>
       </c>
-      <c r="J44" s="1">
+      <c r="L44" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="M44" s="1">
         <v>0</v>
       </c>
       <c r="N44" s="1">
-        <v>0.05625</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
       </c>
       <c r="P44" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q44" s="1">
         <v>0</v>
       </c>
       <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S44" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
       <c r="U44" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
         <v>0</v>
       </c>
     </row>
@@ -28576,58 +28932,66 @@
           <t xml:space="preserve">2023-03</t>
         </is>
       </c>
-      <c r="D45" s="1">
-        <v>0.05625</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
       </c>
       <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="G45" s="1">
         <v>0.064375</v>
-      </c>
-      <c r="F45" s="1">
-        <v>0.025</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0.01125</v>
       </c>
       <c r="H45" s="1">
         <v>0.025</v>
       </c>
       <c r="I45" s="1">
+        <v>0.01125</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="K45" s="1">
         <v>0.030625</v>
       </c>
-      <c r="J45" s="1">
+      <c r="L45" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
       <c r="M45" s="1">
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
       </c>
       <c r="P45" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q45" s="1">
         <v>0</v>
       </c>
       <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S45" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
       <c r="U45" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
         <v>0.5437500000000003</v>
       </c>
     </row>
@@ -28647,58 +29011,66 @@
           <t xml:space="preserve">2023-02</t>
         </is>
       </c>
-      <c r="D46" s="1">
-        <v>0.05625</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
       </c>
       <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="G46" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F46" s="1">
+      <c r="H46" s="1">
         <v>0.025</v>
       </c>
-      <c r="G46" s="1">
+      <c r="I46" s="1">
         <v>0.06900000000000003</v>
       </c>
-      <c r="H46" s="1">
+      <c r="J46" s="1">
         <v>0.16</v>
       </c>
-      <c r="I46" s="1">
+      <c r="K46" s="1">
         <v>0.05687500000000003</v>
       </c>
-      <c r="J46" s="1">
+      <c r="L46" s="1">
         <v>0.05775000000000004</v>
       </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
       <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="N46" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
       <c r="P46" s="1">
-        <v>0.02625000000000003</v>
+        <v>0.05625</v>
       </c>
       <c r="Q46" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="R46" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T46" s="1">
         <v>0.1140000000000003</v>
       </c>
-      <c r="S46" s="1">
+      <c r="U46" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
         <v>0.225</v>
       </c>
     </row>
@@ -28718,58 +29090,66 @@
           <t xml:space="preserve">2023-01</t>
         </is>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E47" s="1">
+      <c r="G47" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F47" s="1">
+      <c r="H47" s="1">
         <v>0.025</v>
       </c>
-      <c r="G47" s="1">
+      <c r="I47" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
         <v>0.05687500000000003</v>
       </c>
-      <c r="J47" s="1">
+      <c r="L47" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
       <c r="M47" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N47" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O47" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P47" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q47" s="1">
         <v>0</v>
       </c>
       <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="S47" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
       <c r="U47" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="1">
         <v>0.43875</v>
       </c>
     </row>
@@ -28789,58 +29169,66 @@
           <t xml:space="preserve">2022-12</t>
         </is>
       </c>
-      <c r="D48" s="1">
-        <v>0.05625</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
       </c>
       <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="G48" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F48" s="1">
+      <c r="H48" s="1">
         <v>0.025</v>
       </c>
-      <c r="G48" s="1">
+      <c r="I48" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H48" s="1">
+      <c r="J48" s="1">
         <v>0.16</v>
       </c>
-      <c r="I48" s="1">
+      <c r="K48" s="1">
         <v>0.03187500000000003</v>
       </c>
-      <c r="J48" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0</v>
-      </c>
       <c r="L48" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M48" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="N48" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O48" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="P48" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="1">
         <v>0.025</v>
       </c>
-      <c r="R48" s="1">
+      <c r="T48" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="S48" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="T48" s="1">
-        <v>0</v>
-      </c>
       <c r="U48" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V48" s="1">
+        <v>0</v>
+      </c>
+      <c r="W48" s="1">
         <v>0.3562499999999997</v>
       </c>
     </row>
@@ -28860,58 +29248,66 @@
           <t xml:space="preserve">2022-11</t>
         </is>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E49" s="1">
+      <c r="G49" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
-      </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
       <c r="L49" s="1">
         <v>0</v>
       </c>
       <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1">
         <v>0.09625000000000003</v>
       </c>
-      <c r="N49" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
       <c r="P49" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
         <v>0.025</v>
       </c>
-      <c r="R49" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
       <c r="T49" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U49" s="1">
+        <v>0</v>
+      </c>
+      <c r="V49" s="1">
+        <v>0</v>
+      </c>
+      <c r="W49" s="1">
         <v>0.6037499999999997</v>
       </c>
     </row>
@@ -28931,30 +29327,32 @@
           <t xml:space="preserve">2022-10</t>
         </is>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E50" s="1">
+      <c r="G50" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F50" s="1">
+      <c r="H50" s="1">
         <v>0.025</v>
       </c>
-      <c r="G50" s="1">
+      <c r="I50" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
       <c r="L50" s="1">
         <v>0</v>
       </c>
@@ -28962,27 +29360,33 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>0.05625</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
         <v>0.025</v>
       </c>
-      <c r="R50" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
       <c r="T50" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
         <v>0.675</v>
       </c>
     </row>
@@ -29002,58 +29406,66 @@
           <t xml:space="preserve">2022-09</t>
         </is>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E51" s="1">
+      <c r="G51" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F51" s="1">
+      <c r="H51" s="1">
         <v>0.025</v>
       </c>
-      <c r="G51" s="1">
+      <c r="I51" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
       <c r="L51" s="1">
         <v>0</v>
       </c>
       <c r="M51" s="1">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>0</v>
+      </c>
+      <c r="O51" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="N51" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
       <c r="P51" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1">
         <v>0.025</v>
       </c>
-      <c r="R51" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
       <c r="T51" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U51" s="1">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
         <v>0.6037499999999997</v>
       </c>
     </row>
@@ -29073,58 +29485,66 @@
           <t xml:space="preserve">2022-08</t>
         </is>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
         <v>0.1075</v>
       </c>
-      <c r="E52" s="1">
+      <c r="G52" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1">
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1">
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
-      </c>
       <c r="L52" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="M52" s="1">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O52" s="1">
         <v>0.1027500000000003</v>
       </c>
-      <c r="N52" s="1">
+      <c r="P52" s="1">
         <v>0.08125</v>
       </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1">
-        <v>0</v>
-      </c>
       <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
         <v>0.025</v>
       </c>
-      <c r="R52" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="T52" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U52" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
         <v>0.4672500000000003</v>
       </c>
     </row>
@@ -29144,58 +29564,66 @@
           <t xml:space="preserve">2022-07</t>
         </is>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E53" s="1">
+      <c r="G53" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F53" s="1">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
-      <c r="I53" s="1">
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J53" s="1">
-        <v>0</v>
-      </c>
-      <c r="K53" s="1">
-        <v>0</v>
-      </c>
       <c r="L53" s="1">
         <v>0</v>
       </c>
       <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="N53" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
       <c r="P53" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
         <v>0.025</v>
       </c>
-      <c r="R53" s="1">
+      <c r="T53" s="1">
         <v>0.08125</v>
       </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="1">
-        <v>0</v>
-      </c>
       <c r="U53" s="1">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
         <v>0.5775000000000003</v>
       </c>
     </row>
@@ -29215,58 +29643,66 @@
           <t xml:space="preserve">2022-06</t>
         </is>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E54" s="1">
+      <c r="G54" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-      <c r="I54" s="1">
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J54" s="1">
-        <v>0</v>
-      </c>
-      <c r="K54" s="1">
-        <v>0</v>
-      </c>
       <c r="L54" s="1">
         <v>0</v>
       </c>
       <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1">
         <v>0.1224999999999997</v>
       </c>
-      <c r="N54" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O54" s="1">
-        <v>0</v>
-      </c>
       <c r="P54" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
         <v>0.025</v>
       </c>
-      <c r="R54" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S54" s="1">
-        <v>0</v>
-      </c>
       <c r="T54" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U54" s="1">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
         <v>0.5775000000000003</v>
       </c>
     </row>
@@ -29286,58 +29722,66 @@
           <t xml:space="preserve">2022-05</t>
         </is>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E55" s="1">
+      <c r="G55" s="1">
         <v>0.064375</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-      <c r="I55" s="1">
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
-      <c r="K55" s="1">
-        <v>0</v>
-      </c>
       <c r="L55" s="1">
         <v>0</v>
       </c>
       <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
         <v>0.1224999999999997</v>
       </c>
-      <c r="N55" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O55" s="1">
-        <v>0</v>
-      </c>
       <c r="P55" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q55" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="T55" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1">
-        <v>0</v>
-      </c>
       <c r="U55" s="1">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
         <v>0.4987500000000004</v>
       </c>
     </row>
@@ -29357,58 +29801,66 @@
           <t xml:space="preserve">2022-04</t>
         </is>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1">
         <v>0.1075</v>
       </c>
-      <c r="E56" s="1">
+      <c r="G56" s="1">
         <v>0.06562500000000003</v>
       </c>
-      <c r="F56" s="1">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1">
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
       <c r="L56" s="1">
-        <v>0.02625000000000003</v>
+        <v>0</v>
       </c>
       <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O56" s="1">
         <v>0.1224999999999997</v>
       </c>
-      <c r="N56" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
       <c r="P56" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
         <v>0.05125000000000003</v>
       </c>
-      <c r="R56" s="1">
+      <c r="T56" s="1">
         <v>0.1337499999999997</v>
       </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
       <c r="U56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
         <v>0.4200000000000003</v>
       </c>
     </row>
@@ -29428,58 +29880,66 @@
           <t xml:space="preserve">2022-03</t>
         </is>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E57" s="1">
+      <c r="G57" s="1">
         <v>0.1281249999999997</v>
       </c>
-      <c r="F57" s="1">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H57" s="1">
+      <c r="J57" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I57" s="1">
+      <c r="K57" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
       <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="M57" s="1">
+      <c r="O57" s="1">
         <v>0.16</v>
       </c>
-      <c r="N57" s="1">
+      <c r="P57" s="1">
         <v>0.09375000000000031</v>
       </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
       <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="R57" s="1">
+      <c r="T57" s="1">
         <v>0.14625</v>
       </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
       <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
         <v>0.1762499999999997</v>
       </c>
     </row>
@@ -29499,58 +29959,66 @@
           <t xml:space="preserve">2022-02</t>
         </is>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
         <v>0.1075</v>
       </c>
-      <c r="E58" s="1">
+      <c r="G58" s="1">
         <v>0.09062500000000004</v>
       </c>
-      <c r="F58" s="1">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
       <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="M58" s="1">
+      <c r="O58" s="1">
         <v>0.1224999999999997</v>
       </c>
-      <c r="N58" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
       <c r="P58" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
         <v>0.025</v>
       </c>
-      <c r="R58" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
       <c r="T58" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
         <v>0.4537500000000003</v>
       </c>
     </row>
@@ -29570,58 +30038,66 @@
           <t xml:space="preserve">2022-01</t>
         </is>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
         <v>0.1674999999999997</v>
       </c>
-      <c r="E59" s="1">
+      <c r="G59" s="1">
         <v>0.1506249999999997</v>
-      </c>
-      <c r="F59" s="1">
-        <v>0.03750000000000003</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0.01125</v>
       </c>
       <c r="H59" s="1">
         <v>0.03750000000000003</v>
       </c>
       <c r="I59" s="1">
+        <v>0.01125</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0.03750000000000003</v>
+      </c>
+      <c r="K59" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J59" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
-      </c>
       <c r="L59" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="M59" s="1">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
         <v>0.0675</v>
       </c>
-      <c r="M59" s="1">
+      <c r="O59" s="1">
         <v>0.1312499999999997</v>
       </c>
-      <c r="N59" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O59" s="1">
+      <c r="P59" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q59" s="1">
         <v>0.0925</v>
       </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1">
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
         <v>0.08624999999999997</v>
       </c>
-      <c r="R59" s="1">
+      <c r="T59" s="1">
         <v>0.1075</v>
       </c>
-      <c r="S59" s="1">
+      <c r="U59" s="1">
         <v>0.0225</v>
       </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
+      <c r="V59" s="1">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29641,58 +30117,66 @@
           <t xml:space="preserve">2021-12</t>
         </is>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
         <v>0.17125</v>
       </c>
-      <c r="E60" s="1">
+      <c r="G60" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F60" s="1">
+      <c r="H60" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G60" s="1">
+      <c r="I60" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-      <c r="I60" s="1">
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
       <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
         <v>0.09749999999999971</v>
       </c>
-      <c r="M60" s="1">
+      <c r="O60" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="N60" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O60" s="1">
+      <c r="P60" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q60" s="1">
         <v>0.135</v>
       </c>
-      <c r="P60" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="Q60" s="1">
+      <c r="R60" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="S60" s="1">
         <v>0.08874999999999997</v>
       </c>
-      <c r="R60" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="T60" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U60" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29712,58 +30196,66 @@
           <t xml:space="preserve">2021-11</t>
         </is>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
         <v>0.1674999999999997</v>
       </c>
-      <c r="E61" s="1">
+      <c r="G61" s="1">
         <v>0.1506249999999997</v>
       </c>
-      <c r="F61" s="1">
+      <c r="H61" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G61" s="1">
+      <c r="I61" s="1">
         <v>0.03375</v>
       </c>
-      <c r="H61" s="1">
+      <c r="J61" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I61" s="1">
+      <c r="K61" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J61" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
       <c r="L61" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
         <v>0.0675</v>
       </c>
-      <c r="M61" s="1">
+      <c r="O61" s="1">
         <v>0.1312499999999997</v>
       </c>
-      <c r="N61" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O61" s="1">
+      <c r="P61" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q61" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="P61" s="1">
+      <c r="R61" s="1">
         <v>0.0225</v>
       </c>
-      <c r="Q61" s="1">
+      <c r="S61" s="1">
         <v>0.08874999999999997</v>
       </c>
-      <c r="R61" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S61" s="1">
+      <c r="T61" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="U61" s="1">
         <v>0.0225</v>
       </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
+      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29783,58 +30275,66 @@
           <t xml:space="preserve">2021-10</t>
         </is>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="E62" s="1">
+      <c r="G62" s="1">
         <v>0.1596249999999997</v>
       </c>
-      <c r="F62" s="1">
+      <c r="H62" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G62" s="1">
+      <c r="I62" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H62" s="1">
+      <c r="J62" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I62" s="1">
+      <c r="K62" s="1">
         <v>0.005625000000000001</v>
       </c>
-      <c r="J62" s="1">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
       <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
         <v>0.1027500000000003</v>
       </c>
-      <c r="M62" s="1">
+      <c r="O62" s="1">
         <v>0.1652499999999997</v>
       </c>
-      <c r="N62" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O62" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="P62" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="R62" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="Q62" s="1">
+      <c r="S62" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="R62" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S62" s="1">
+      <c r="T62" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="U62" s="1">
         <v>0.03150000000000001</v>
       </c>
-      <c r="T62" s="1">
-        <v>0</v>
-      </c>
-      <c r="U62" s="1">
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29854,58 +30354,66 @@
           <t xml:space="preserve">2021-09</t>
         </is>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E63" s="1">
+      <c r="G63" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F63" s="1">
+      <c r="H63" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G63" s="1">
+      <c r="I63" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H63" s="1">
+      <c r="J63" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I63" s="1">
+      <c r="K63" s="1">
         <v>0.05687500000000003</v>
       </c>
-      <c r="J63" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K63" s="1">
-        <v>0</v>
-      </c>
       <c r="L63" s="1">
         <v>0.02625000000000003</v>
       </c>
       <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="O63" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="N63" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="P63" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q63" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R63" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S63" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="T63" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U63" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29925,58 +30433,66 @@
           <t xml:space="preserve">2021-08</t>
         </is>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="E64" s="1">
+      <c r="G64" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F64" s="1">
+      <c r="H64" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G64" s="1">
+      <c r="I64" s="1">
         <v>0.01125</v>
       </c>
-      <c r="H64" s="1">
+      <c r="J64" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I64" s="1">
+      <c r="K64" s="1">
         <v>0.03187500000000003</v>
       </c>
-      <c r="J64" s="1">
+      <c r="L64" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="M64" s="1">
+      <c r="O64" s="1">
         <v>0.16</v>
       </c>
-      <c r="N64" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="P64" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="R64" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="Q64" s="1">
+      <c r="S64" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R64" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S64" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="T64" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U64" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
         <v>0</v>
       </c>
     </row>
@@ -29996,58 +30512,66 @@
           <t xml:space="preserve">2021-07</t>
         </is>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
         <v>0.30625</v>
       </c>
-      <c r="E65" s="1">
+      <c r="G65" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F65" s="1">
+      <c r="H65" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G65" s="1">
+      <c r="I65" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-      <c r="I65" s="1">
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J65" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
       <c r="L65" s="1">
-        <v>0</v>
+        <v>0.02625000000000003</v>
       </c>
       <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1">
         <v>0.115</v>
       </c>
-      <c r="N65" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
       <c r="P65" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
         <v>0.06374999999999997</v>
       </c>
-      <c r="R65" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0.02625000000000003</v>
-      </c>
       <c r="T65" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="U65" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30067,58 +30591,66 @@
           <t xml:space="preserve">2021-06</t>
         </is>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
         <v>0.08125</v>
       </c>
-      <c r="E66" s="1">
+      <c r="G66" s="1">
         <v>0.129375</v>
       </c>
-      <c r="F66" s="1">
+      <c r="H66" s="1">
         <v>0.06250000000000003</v>
       </c>
-      <c r="G66" s="1">
+      <c r="I66" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H66" s="1">
+      <c r="J66" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="I66" s="1">
+      <c r="K66" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J66" s="1">
+      <c r="L66" s="1">
         <v>0.05249999999999997</v>
       </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
         <v>0.04500000000000001</v>
       </c>
-      <c r="M66" s="1">
+      <c r="O66" s="1">
         <v>0.16</v>
       </c>
-      <c r="N66" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
       <c r="P66" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R66" s="1">
+      <c r="T66" s="1">
         <v>0.1075</v>
       </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
       <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
@@ -30138,79 +30670,89 @@
           <t xml:space="preserve">2021-05</t>
         </is>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1">
         <v>0.1449999999999997</v>
       </c>
-      <c r="E67" s="1">
+      <c r="G67" s="1">
         <v>0.154375</v>
       </c>
-      <c r="F67" s="1">
+      <c r="H67" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="G67" s="1">
+      <c r="I67" s="1">
         <v>0.03750000000000003</v>
       </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1">
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
         <v>0.095625</v>
       </c>
-      <c r="J67" s="1">
-        <v>0.02625000000000003</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
       <c r="L67" s="1">
+        <v>0.02625000000000003</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
         <v>0.07125000000000004</v>
       </c>
-      <c r="M67" s="1">
+      <c r="O67" s="1">
         <v>0.16</v>
       </c>
-      <c r="N67" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
       <c r="P67" s="1">
-        <v>0</v>
+        <v>0.05625</v>
       </c>
       <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
         <v>0.09000000000000001</v>
       </c>
-      <c r="R67" s="1">
+      <c r="T67" s="1">
         <v>0.08125</v>
       </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
       <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U67"/>
+  <autoFilter ref="A1:W67"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30231,20 +30773,30 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">State</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk Budget</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Equity</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fixed Income</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Real Assets / Other</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cash</t>
         </is>
@@ -30266,17 +30818,25 @@
           <t xml:space="preserve">2026-10</t>
         </is>
       </c>
-      <c r="D2" s="1">
-        <v>0.2675327644050124</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
       </c>
       <c r="E2" s="1">
-        <v>0.03876038119196892</v>
+        <v>0.6890736222267151</v>
       </c>
       <c r="F2" s="1">
-        <v>0.165722163140774</v>
+        <v>0.2675328338295225</v>
       </c>
       <c r="G2" s="1">
-        <v>0.5279846912622452</v>
+        <v>0.03876039125025273</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.1657222061455252</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.5279845687747001</v>
       </c>
     </row>
     <row r="3">
@@ -30295,16 +30855,24 @@
           <t xml:space="preserve">2026-09</t>
         </is>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
         <v>0.4087500000000004</v>
       </c>
-      <c r="E3" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H3" s="1">
         <v>0.2200000000000003</v>
       </c>
-      <c r="G3" s="1">
+      <c r="I3" s="1">
         <v>0.315</v>
       </c>
     </row>
@@ -30324,16 +30892,24 @@
           <t xml:space="preserve">2026-08</t>
         </is>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.4962499999999999</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>0.33125</v>
       </c>
-      <c r="G4" s="1">
+      <c r="I4" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -30353,16 +30929,24 @@
           <t xml:space="preserve">2026-07</t>
         </is>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
+      </c>
+      <c r="E5" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.4252874999999995</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>0.04826250000000001</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>0.07645000000000003</v>
       </c>
-      <c r="G5" s="1">
+      <c r="I5" s="1">
         <v>0.45</v>
       </c>
     </row>
@@ -30382,17 +30966,25 @@
           <t xml:space="preserve">2026-06</t>
         </is>
       </c>
-      <c r="D6" s="1">
-        <v>0.4184788304421563</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
       </c>
       <c r="E6" s="1">
-        <v>0.0479506993214971</v>
+        <v>0.581220578710214</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1147910680726749</v>
+        <v>0.4184788166713541</v>
       </c>
       <c r="G6" s="1">
-        <v>0.4187794021636717</v>
+        <v>0.04795069774359267</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.1147910642952673</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.418779421289786</v>
       </c>
     </row>
     <row r="7">
@@ -30411,16 +31003,24 @@
           <t xml:space="preserve">2026-05</t>
         </is>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
         <v>0.6687499999999997</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>0.2487500000000001</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30440,16 +31040,24 @@
           <t xml:space="preserve">2026-04</t>
         </is>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
         <v>0.4282499999999998</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>0.144</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>0.2852499999999994</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>0.1424999999999997</v>
       </c>
     </row>
@@ -30469,16 +31077,24 @@
           <t xml:space="preserve">2026-03</t>
         </is>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>0.6812499999999999</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>0.23625</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30498,16 +31114,24 @@
           <t xml:space="preserve">2026-02</t>
         </is>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
         <v>0.6562499999999994</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>0.235</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30527,16 +31151,24 @@
           <t xml:space="preserve">2026-01</t>
         </is>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
         <v>0.7199999999999994</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>0.1975</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30556,16 +31188,24 @@
           <t xml:space="preserve">2025-12</t>
         </is>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
         <v>0.7187499999999994</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>0.19875</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30585,16 +31225,24 @@
           <t xml:space="preserve">2025-11</t>
         </is>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
         <v>0.7187499999999997</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>0.1725</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30614,16 +31262,24 @@
           <t xml:space="preserve">2025-10</t>
         </is>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
         <v>0.7357499999999992</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>0.08775000000000001</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>0.1764999999999997</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30643,16 +31299,24 @@
           <t xml:space="preserve">2025-09</t>
         </is>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
         <v>0.7462500000000001</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>0.17125</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30672,16 +31336,24 @@
           <t xml:space="preserve">2025-08</t>
         </is>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
         <v>0.7462499999999999</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>0.17125</v>
       </c>
-      <c r="G16" s="1">
+      <c r="I16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30701,16 +31373,24 @@
           <t xml:space="preserve">2025-07</t>
         </is>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
         <v>0.7199999999999996</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>0.17125</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30730,18 +31410,26 @@
           <t xml:space="preserve">2025-06</t>
         </is>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
         <v>0.5587500000000001</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.135</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0.17125</v>
       </c>
       <c r="G18" s="1">
         <v>0.135</v>
       </c>
+      <c r="H18" s="1">
+        <v>0.17125</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.135</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30759,16 +31447,24 @@
           <t xml:space="preserve">2025-05</t>
         </is>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
         <v>0.3375000000000001</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>0.4537500000000001</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>0.20875</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30788,16 +31484,24 @@
           <t xml:space="preserve">2025-04</t>
         </is>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
         <v>0.31125</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>0.345</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>0.3437500000000001</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30817,16 +31521,24 @@
           <t xml:space="preserve">2025-03</t>
         </is>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
         <v>0.5662499999999997</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>0.135</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>0.2987500000000001</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30846,16 +31558,24 @@
           <t xml:space="preserve">2025-02</t>
         </is>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
         <v>0.6675000000000001</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>0.10875</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>0.22375</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -30875,16 +31595,24 @@
           <t xml:space="preserve">2025-01</t>
         </is>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
         <v>0.3030000000000006</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>0.114</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>0.1705000000000003</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>0.4124999999999997</v>
       </c>
     </row>
@@ -30904,16 +31632,24 @@
           <t xml:space="preserve">2024-12</t>
         </is>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
         <v>0.4529999999999995</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>0.2302500000000001</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>0.2402499999999997</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>0.07650000000000001</v>
       </c>
     </row>
@@ -30933,16 +31669,24 @@
           <t xml:space="preserve">2024-11</t>
         </is>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
         <v>0.4950000000000001</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>0.15375</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>0.26125</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -30962,16 +31706,24 @@
           <t xml:space="preserve">2024-10</t>
         </is>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEFENSIVE</t>
+        </is>
+      </c>
+      <c r="E26" s="1">
+        <v>0.55</v>
+      </c>
+      <c r="F26" s="1">
         <v>0.3609375</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>0.04537500000000002</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>0.1436875</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>0.45</v>
       </c>
     </row>
@@ -30991,16 +31743,24 @@
           <t xml:space="preserve">2024-09</t>
         </is>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
         <v>0.6812499999999998</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>0.23625</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31020,16 +31780,24 @@
           <t xml:space="preserve">2024-08</t>
         </is>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
         <v>0.6825000000000001</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>0.235</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31049,16 +31817,24 @@
           <t xml:space="preserve">2024-07</t>
         </is>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
         <v>0.6719999999999992</v>
       </c>
-      <c r="E29" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H29" s="1">
         <v>0.2717499999999994</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31078,16 +31854,24 @@
           <t xml:space="preserve">2024-06</t>
         </is>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
         <v>0.7094999999999992</v>
       </c>
-      <c r="E30" s="1">
+      <c r="G30" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F30" s="1">
+      <c r="H30" s="1">
         <v>0.2079999999999997</v>
       </c>
-      <c r="G30" s="1">
+      <c r="I30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31107,16 +31891,24 @@
           <t xml:space="preserve">2024-05</t>
         </is>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
         <v>0.4132500000000008</v>
       </c>
-      <c r="E31" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H31" s="1">
         <v>0.2155000000000003</v>
       </c>
-      <c r="G31" s="1">
+      <c r="I31" s="1">
         <v>0.315</v>
       </c>
     </row>
@@ -31136,16 +31928,24 @@
           <t xml:space="preserve">2024-04</t>
         </is>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
         <v>0.6925000000000001</v>
       </c>
-      <c r="E32" s="1">
+      <c r="G32" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F32" s="1">
+      <c r="H32" s="1">
         <v>0.1987500000000001</v>
       </c>
-      <c r="G32" s="1">
+      <c r="I32" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31165,16 +31965,24 @@
           <t xml:space="preserve">2024-03</t>
         </is>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
         <v>0.6225000000000001</v>
       </c>
-      <c r="E33" s="1">
+      <c r="G33" s="1">
         <v>0.1537500000000001</v>
       </c>
-      <c r="F33" s="1">
+      <c r="H33" s="1">
         <v>0.1337500000000001</v>
       </c>
-      <c r="G33" s="1">
+      <c r="I33" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -31194,16 +32002,24 @@
           <t xml:space="preserve">2024-02</t>
         </is>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
         <v>0.4937500000000001</v>
       </c>
-      <c r="E34" s="1">
+      <c r="G34" s="1">
         <v>0.3412500000000001</v>
       </c>
-      <c r="F34" s="1">
+      <c r="H34" s="1">
         <v>0.1199999999999997</v>
       </c>
-      <c r="G34" s="1">
+      <c r="I34" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
@@ -31223,16 +32039,24 @@
           <t xml:space="preserve">2024-01</t>
         </is>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
         <v>0.6937500000000001</v>
       </c>
-      <c r="E35" s="1">
+      <c r="G35" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F35" s="1">
+      <c r="H35" s="1">
         <v>0.1974999999999997</v>
       </c>
-      <c r="G35" s="1">
+      <c r="I35" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31252,16 +32076,24 @@
           <t xml:space="preserve">2023-12</t>
         </is>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
         <v>0.7357499999999991</v>
       </c>
-      <c r="E36" s="1">
+      <c r="G36" s="1">
         <v>0.08775000000000001</v>
       </c>
-      <c r="F36" s="1">
+      <c r="H36" s="1">
         <v>0.1765000000000003</v>
       </c>
-      <c r="G36" s="1">
+      <c r="I36" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31281,16 +32113,24 @@
           <t xml:space="preserve">2023-11</t>
         </is>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
         <v>0.2400000000000001</v>
       </c>
-      <c r="E37" s="1">
+      <c r="G37" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F37" s="1">
+      <c r="H37" s="1">
         <v>0.1862499999999997</v>
       </c>
-      <c r="G37" s="1">
+      <c r="I37" s="1">
         <v>0.4912499999999997</v>
       </c>
     </row>
@@ -31310,16 +32150,24 @@
           <t xml:space="preserve">2023-10</t>
         </is>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
         <v>0.3174999999999998</v>
       </c>
-      <c r="E38" s="1">
+      <c r="G38" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F38" s="1">
+      <c r="H38" s="1">
         <v>0.1799999999999997</v>
       </c>
-      <c r="G38" s="1">
+      <c r="I38" s="1">
         <v>0.4200000000000003</v>
       </c>
     </row>
@@ -31339,16 +32187,24 @@
           <t xml:space="preserve">2023-09</t>
         </is>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
         <v>0.3699999999999994</v>
       </c>
-      <c r="E39" s="1">
+      <c r="G39" s="1">
         <v>0.10875</v>
       </c>
-      <c r="F39" s="1">
+      <c r="H39" s="1">
         <v>0.1612499999999997</v>
       </c>
-      <c r="G39" s="1">
+      <c r="I39" s="1">
         <v>0.36</v>
       </c>
     </row>
@@ -31368,16 +32224,24 @@
           <t xml:space="preserve">2023-08</t>
         </is>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
         <v>0.4697500000000007</v>
       </c>
-      <c r="E40" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H40" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="G40" s="1">
+      <c r="I40" s="1">
         <v>0.3915</v>
       </c>
     </row>
@@ -31397,16 +32261,24 @@
           <t xml:space="preserve">2023-07</t>
         </is>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
         <v>0.4224999999999995</v>
       </c>
-      <c r="E41" s="1">
+      <c r="G41" s="1">
         <v>0.1275</v>
       </c>
-      <c r="F41" s="1">
+      <c r="H41" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="G41" s="1">
+      <c r="I41" s="1">
         <v>0.3412500000000003</v>
       </c>
     </row>
@@ -31426,16 +32298,24 @@
           <t xml:space="preserve">2023-06</t>
         </is>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
         <v>0.3962499999999994</v>
       </c>
-      <c r="E42" s="1">
+      <c r="G42" s="1">
         <v>0.10875</v>
       </c>
-      <c r="F42" s="1">
+      <c r="H42" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="G42" s="1">
+      <c r="I42" s="1">
         <v>0.3862500000000003</v>
       </c>
     </row>
@@ -31455,16 +32335,24 @@
           <t xml:space="preserve">2023-05</t>
         </is>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
         <v>0.54625</v>
       </c>
-      <c r="E43" s="1">
+      <c r="G43" s="1">
         <v>0.2175000000000004</v>
       </c>
-      <c r="F43" s="1">
+      <c r="H43" s="1">
         <v>0.14625</v>
       </c>
-      <c r="G43" s="1">
+      <c r="I43" s="1">
         <v>0.09000000000000001</v>
       </c>
     </row>
@@ -31484,16 +32372,24 @@
           <t xml:space="preserve">2023-04</t>
         </is>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
         <v>0.7450000000000002</v>
       </c>
-      <c r="E44" s="1">
+      <c r="G44" s="1">
         <v>0.1087500000000001</v>
       </c>
-      <c r="F44" s="1">
+      <c r="H44" s="1">
         <v>0.14625</v>
       </c>
-      <c r="G44" s="1">
+      <c r="I44" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31513,16 +32409,24 @@
           <t xml:space="preserve">2023-03</t>
         </is>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
         <v>0.265</v>
       </c>
-      <c r="E45" s="1">
+      <c r="G45" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F45" s="1">
+      <c r="H45" s="1">
         <v>0.1087499999999997</v>
       </c>
-      <c r="G45" s="1">
+      <c r="I45" s="1">
         <v>0.5437500000000003</v>
       </c>
     </row>
@@ -31542,16 +32446,24 @@
           <t xml:space="preserve">2023-02</t>
         </is>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
         <v>0.4892500000000001</v>
       </c>
-      <c r="E46" s="1">
+      <c r="G46" s="1">
         <v>0.114</v>
       </c>
-      <c r="F46" s="1">
+      <c r="H46" s="1">
         <v>0.1717500000000003</v>
       </c>
-      <c r="G46" s="1">
+      <c r="I46" s="1">
         <v>0.225</v>
       </c>
     </row>
@@ -31571,16 +32483,24 @@
           <t xml:space="preserve">2023-01</t>
         </is>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
         <v>0.3437500000000001</v>
       </c>
-      <c r="E47" s="1">
+      <c r="G47" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F47" s="1">
+      <c r="H47" s="1">
         <v>0.1349999999999997</v>
       </c>
-      <c r="G47" s="1">
+      <c r="I47" s="1">
         <v>0.43875</v>
       </c>
     </row>
@@ -31600,16 +32520,24 @@
           <t xml:space="preserve">2022-12</t>
         </is>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
         <v>0.4275000000000002</v>
       </c>
-      <c r="E48" s="1">
+      <c r="G48" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F48" s="1">
+      <c r="H48" s="1">
         <v>0.1337500000000001</v>
       </c>
-      <c r="G48" s="1">
+      <c r="I48" s="1">
         <v>0.3562499999999997</v>
       </c>
     </row>
@@ -31629,16 +32557,24 @@
           <t xml:space="preserve">2022-11</t>
         </is>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
         <v>0.1625</v>
       </c>
-      <c r="E49" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H49" s="1">
         <v>0.1775</v>
       </c>
-      <c r="G49" s="1">
+      <c r="I49" s="1">
         <v>0.6037499999999997</v>
       </c>
     </row>
@@ -31658,16 +32594,24 @@
           <t xml:space="preserve">2022-10</t>
         </is>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
         <v>0.1875</v>
       </c>
-      <c r="E50" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H50" s="1">
         <v>0.08125</v>
       </c>
-      <c r="G50" s="1">
+      <c r="I50" s="1">
         <v>0.675</v>
       </c>
     </row>
@@ -31687,16 +32631,24 @@
           <t xml:space="preserve">2022-09</t>
         </is>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1">
         <v>0.1875</v>
       </c>
-      <c r="E51" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F51" s="1">
+      <c r="G51" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H51" s="1">
         <v>0.1525</v>
       </c>
-      <c r="G51" s="1">
+      <c r="I51" s="1">
         <v>0.6037499999999997</v>
       </c>
     </row>
@@ -31716,16 +32668,24 @@
           <t xml:space="preserve">2022-08</t>
         </is>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
         <v>0.2150000000000001</v>
       </c>
-      <c r="E52" s="1">
+      <c r="G52" s="1">
         <v>0.1337500000000001</v>
       </c>
-      <c r="F52" s="1">
+      <c r="H52" s="1">
         <v>0.1840000000000003</v>
       </c>
-      <c r="G52" s="1">
+      <c r="I52" s="1">
         <v>0.4672500000000003</v>
       </c>
     </row>
@@ -31745,16 +32705,24 @@
           <t xml:space="preserve">2022-07</t>
         </is>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
         <v>0.1625</v>
       </c>
-      <c r="E53" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H53" s="1">
         <v>0.2037499999999997</v>
       </c>
-      <c r="G53" s="1">
+      <c r="I53" s="1">
         <v>0.5775000000000003</v>
       </c>
     </row>
@@ -31774,16 +32742,24 @@
           <t xml:space="preserve">2022-06</t>
         </is>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
         <v>0.1625</v>
       </c>
-      <c r="E54" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F54" s="1">
+      <c r="G54" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H54" s="1">
         <v>0.2037499999999997</v>
       </c>
-      <c r="G54" s="1">
+      <c r="I54" s="1">
         <v>0.5775000000000003</v>
       </c>
     </row>
@@ -31803,16 +32779,24 @@
           <t xml:space="preserve">2022-05</t>
         </is>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1">
         <v>0.1625</v>
       </c>
-      <c r="E55" s="1">
-        <v>0.05625</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="G55" s="1">
+        <v>0.05625</v>
+      </c>
+      <c r="H55" s="1">
         <v>0.2824999999999994</v>
       </c>
-      <c r="G55" s="1">
+      <c r="I55" s="1">
         <v>0.4987500000000004</v>
       </c>
     </row>
@@ -31832,16 +32816,24 @@
           <t xml:space="preserve">2022-04</t>
         </is>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1">
         <v>0.1900000000000001</v>
       </c>
-      <c r="E56" s="1">
+      <c r="G56" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F56" s="1">
+      <c r="H56" s="1">
         <v>0.3074999999999994</v>
       </c>
-      <c r="G56" s="1">
+      <c r="I56" s="1">
         <v>0.4200000000000003</v>
       </c>
     </row>
@@ -31861,16 +32853,24 @@
           <t xml:space="preserve">2022-03</t>
         </is>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
         <v>0.2637499999999997</v>
       </c>
-      <c r="E57" s="1">
+      <c r="G57" s="1">
         <v>0.19125</v>
       </c>
-      <c r="F57" s="1">
+      <c r="H57" s="1">
         <v>0.36875</v>
       </c>
-      <c r="G57" s="1">
+      <c r="I57" s="1">
         <v>0.1762499999999997</v>
       </c>
     </row>
@@ -31890,16 +32890,24 @@
           <t xml:space="preserve">2022-02</t>
         </is>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
         <v>0.2150000000000001</v>
       </c>
-      <c r="E58" s="1">
+      <c r="G58" s="1">
         <v>0.1275</v>
       </c>
-      <c r="F58" s="1">
+      <c r="H58" s="1">
         <v>0.2037499999999997</v>
       </c>
-      <c r="G58" s="1">
+      <c r="I58" s="1">
         <v>0.4537500000000003</v>
       </c>
     </row>
@@ -31919,16 +32927,24 @@
           <t xml:space="preserve">2022-01</t>
         </is>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
         <v>0.4362499999999995</v>
       </c>
-      <c r="E59" s="1">
+      <c r="G59" s="1">
         <v>0.23875</v>
       </c>
-      <c r="F59" s="1">
+      <c r="H59" s="1">
         <v>0.3249999999999997</v>
       </c>
-      <c r="G59" s="1">
+      <c r="I59" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31948,16 +32964,24 @@
           <t xml:space="preserve">2021-12</t>
         </is>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
         <v>0.405</v>
       </c>
-      <c r="E60" s="1">
+      <c r="G60" s="1">
         <v>0.3412499999999998</v>
       </c>
-      <c r="F60" s="1">
+      <c r="H60" s="1">
         <v>0.2537499999999997</v>
       </c>
-      <c r="G60" s="1">
+      <c r="I60" s="1">
         <v>0</v>
       </c>
     </row>
@@ -31977,16 +33001,24 @@
           <t xml:space="preserve">2021-11</t>
         </is>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
         <v>0.4837499999999995</v>
       </c>
-      <c r="E61" s="1">
+      <c r="G61" s="1">
         <v>0.24</v>
       </c>
-      <c r="F61" s="1">
+      <c r="H61" s="1">
         <v>0.2762499999999997</v>
       </c>
-      <c r="G61" s="1">
+      <c r="I61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32006,16 +33038,24 @@
           <t xml:space="preserve">2021-10</t>
         </is>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
         <v>0.4529999999999995</v>
       </c>
-      <c r="E62" s="1">
+      <c r="G62" s="1">
         <v>0.2617500000000004</v>
       </c>
-      <c r="F62" s="1">
+      <c r="H62" s="1">
         <v>0.2852499999999997</v>
       </c>
-      <c r="G62" s="1">
+      <c r="I62" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32035,16 +33075,24 @@
           <t xml:space="preserve">2021-09</t>
         </is>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
         <v>0.6550000000000001</v>
       </c>
-      <c r="E63" s="1">
+      <c r="G63" s="1">
         <v>0.1350000000000001</v>
       </c>
-      <c r="F63" s="1">
+      <c r="H63" s="1">
         <v>0.21</v>
       </c>
-      <c r="G63" s="1">
+      <c r="I63" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32064,16 +33112,24 @@
           <t xml:space="preserve">2021-08</t>
         </is>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
         <v>0.4949999999999998</v>
       </c>
-      <c r="E64" s="1">
+      <c r="G64" s="1">
         <v>0.1987500000000001</v>
       </c>
-      <c r="F64" s="1">
+      <c r="H64" s="1">
         <v>0.30625</v>
       </c>
-      <c r="G64" s="1">
+      <c r="I64" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32093,16 +33149,24 @@
           <t xml:space="preserve">2021-07</t>
         </is>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
         <v>0.6825000000000001</v>
       </c>
-      <c r="E65" s="1">
+      <c r="G65" s="1">
         <v>0.08250000000000003</v>
       </c>
-      <c r="F65" s="1">
+      <c r="H65" s="1">
         <v>0.235</v>
       </c>
-      <c r="G65" s="1">
+      <c r="I65" s="1">
         <v>0</v>
       </c>
     </row>
@@ -32122,16 +33186,24 @@
           <t xml:space="preserve">2021-06</t>
         </is>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
         <v>0.4962500000000001</v>
       </c>
-      <c r="E66" s="1">
+      <c r="G66" s="1">
         <v>0.10125</v>
       </c>
-      <c r="F66" s="1">
+      <c r="H66" s="1">
         <v>0.3575</v>
       </c>
-      <c r="G66" s="1">
+      <c r="I66" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
@@ -32151,21 +33223,29 @@
           <t xml:space="preserve">2021-05</t>
         </is>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1">
         <v>0.4962499999999999</v>
       </c>
-      <c r="E67" s="1">
+      <c r="G67" s="1">
         <v>0.1275</v>
       </c>
-      <c r="F67" s="1">
+      <c r="H67" s="1">
         <v>0.33125</v>
       </c>
-      <c r="G67" s="1">
+      <c r="I67" s="1">
         <v>0.04500000000000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G67"/>
+  <autoFilter ref="A1:I67"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -32322,25 +33402,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.1173906043171885</v>
+        <v>0.117390616744757</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0554227223619819</v>
+        <v>0.05542272822931411</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03167012706398967</v>
+        <v>0.03167013041675094</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.07463593278080229</v>
+        <v>0.07463594068214301</v>
       </c>
       <c r="J2" s="1">
-        <v>0.04877199567854408</v>
+        <v>0.04877200084179643</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -32349,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1078895661979916</v>
+        <v>0.1078895776197317</v>
       </c>
       <c r="N2" s="1">
-        <v>0.04750519059598446</v>
+        <v>0.04750519562512637</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -32364,7 +33444,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.09522151537239554</v>
+        <v>0.09522152545303109</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -32373,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4214923456311226</v>
+        <v>0.4214922843873501</v>
       </c>
     </row>
     <row r="3">
@@ -32606,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920136897356</v>
+        <v>0.1353920120520621</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504648954916</v>
+        <v>0.1220504634191946</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788620943118</v>
+        <v>0.02964788585081654</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281627728142</v>
+        <v>0.1660281607645722</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736730700356</v>
+        <v>0.0953673661534598</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075352034660183</v>
+        <v>0.02075352009557158</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -32633,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492690263478</v>
+        <v>0.07115492604195964</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182931414673</v>
+        <v>0.04447182877622477</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -32648,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060713370268</v>
+        <v>0.08499060610567404</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075352034660183</v>
+        <v>0.02075352009557158</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897010818359</v>
+        <v>0.209389710644893</v>
       </c>
     </row>
     <row r="7">
@@ -37065,16 +38145,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3278913822025065</v>
+        <v>0.3278914169147615</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04750519059598446</v>
+        <v>0.04750519562512637</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2031110815703872</v>
+        <v>0.2031111030727628</v>
       </c>
       <c r="G2" s="1">
-        <v>0.4214923456311226</v>
+        <v>0.4214922843873501</v>
       </c>
     </row>
     <row r="3">
@@ -37181,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.569239415221078</v>
+        <v>0.5692394083356769</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522534966074857</v>
+        <v>0.06522534887179635</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455340363375</v>
+        <v>0.1561455321476337</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897010818359</v>
+        <v>0.209389710644893</v>
       </c>
     </row>
     <row r="7">
@@ -38970,7 +40050,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -39112,10 +40192,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adaptive Risk Budget</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fraction of the Core target retained by the fixed Adaptive policy; residual allocation is held in BIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Workbook purpose</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">Fixed-universe target and asset-class history for monitoring; not a historical live-policy claim</t>
         </is>

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25541,28 +25541,28 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890736222267151</v>
+        <v>0.6890733242034912</v>
       </c>
       <c r="F2" s="1">
-        <v>0.09578123348951362</v>
+        <v>0.09578119206428549</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0452204564586282</v>
+        <v>0.04522043690085413</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.02584026083350184</v>
+        <v>0.02584024965763094</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.06089688136428597</v>
+        <v>0.06089685502648356</v>
       </c>
       <c r="L2" s="1">
-        <v>0.03979400168359282</v>
+        <v>0.03979398447275164</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -25571,10 +25571,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0.08802915523946306</v>
+        <v>0.08802911716699621</v>
       </c>
       <c r="P2" s="1">
-        <v>0.03876039125025273</v>
+        <v>0.03876037448644638</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="1">
-        <v>0.07769305090606214</v>
+        <v>0.07769301730394365</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
@@ -25595,7 +25595,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.5279845687747001</v>
+        <v>0.5279847729206085</v>
       </c>
     </row>
     <row r="3">
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.581220578710214</v>
+        <v>0.5812205444138646</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953402410412417</v>
+        <v>0.09953401823087432</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972592683838929</v>
+        <v>0.08972592154389034</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179577170163305</v>
+        <v>0.02179577041551994</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563215291448</v>
+        <v>0.1220563143269114</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010973230691958</v>
+        <v>0.07010972816992242</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525704019114314</v>
+        <v>0.01525703929086396</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230985208391927</v>
+        <v>0.05230984899724782</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365755244954</v>
+        <v>0.03269365562327989</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248121221134803</v>
+        <v>0.06248120852449047</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525704019114314</v>
+        <v>0.01525703929086396</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.418779421289786</v>
+        <v>0.4187794555861354</v>
       </c>
     </row>
     <row r="7">
@@ -30824,19 +30824,19 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890736222267151</v>
+        <v>0.6890733242034912</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2675328338295225</v>
+        <v>0.2675327181220057</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03876039125025273</v>
+        <v>0.03876037448644638</v>
       </c>
       <c r="H2" s="1">
-        <v>0.1657222061455252</v>
+        <v>0.1657221344709399</v>
       </c>
       <c r="I2" s="1">
-        <v>0.5279845687747001</v>
+        <v>0.5279847729206085</v>
       </c>
     </row>
     <row r="3">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.581220578710214</v>
+        <v>0.5812205444138646</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184788166713541</v>
+        <v>0.4184787919779824</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795069774359267</v>
+        <v>0.04795069491414385</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910642952673</v>
+        <v>0.1147910575217383</v>
       </c>
       <c r="I6" s="1">
-        <v>0.418779421289786</v>
+        <v>0.4187794555861354</v>
       </c>
     </row>
     <row r="7">
@@ -33402,25 +33402,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.117390616744757</v>
+        <v>0.1173905960321429</v>
       </c>
       <c r="E2" s="1">
-        <v>0.05542272822931411</v>
+        <v>0.05542271845042708</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03167013041675094</v>
+        <v>0.03167012482881549</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.07463594068214301</v>
+        <v>0.0746359275132418</v>
       </c>
       <c r="J2" s="1">
-        <v>0.04877200084179643</v>
+        <v>0.04877199223637584</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1078895776197317</v>
+        <v>0.1078895585834983</v>
       </c>
       <c r="N2" s="1">
-        <v>0.04750519562512637</v>
+        <v>0.0475051872432232</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -33444,7 +33444,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.09522152545303109</v>
+        <v>0.09522150865197183</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -33453,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4214922843873501</v>
+        <v>0.4214923864603043</v>
       </c>
     </row>
     <row r="3">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920120520621</v>
+        <v>0.1353920091154372</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504634191946</v>
+        <v>0.1220504607719452</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788585081654</v>
+        <v>0.02964788520775999</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281607645722</v>
+        <v>0.1660281571634556</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0953673661534598</v>
+        <v>0.09536736408496121</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075352009557158</v>
+        <v>0.020753519645432</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492604195964</v>
+        <v>0.07115492449862391</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182877622477</v>
+        <v>0.04447182781163994</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060610567404</v>
+        <v>0.08499060426224525</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075352009557158</v>
+        <v>0.020753519645432</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.209389710644893</v>
+        <v>0.2093897277930677</v>
       </c>
     </row>
     <row r="7">
@@ -38145,16 +38145,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3278914169147615</v>
+        <v>0.3278913590610031</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04750519562512637</v>
+        <v>0.0475051872432232</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2031111030727628</v>
+        <v>0.2031110672354701</v>
       </c>
       <c r="G2" s="1">
-        <v>0.4214922843873501</v>
+        <v>0.4214923864603043</v>
       </c>
     </row>
     <row r="3">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692394083356769</v>
+        <v>0.5692393959889912</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522534887179635</v>
+        <v>0.06522534745707194</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455321476337</v>
+        <v>0.1561455287608692</v>
       </c>
       <c r="G6" s="1">
-        <v>0.209389710644893</v>
+        <v>0.2093897277930677</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25541,28 +25541,28 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890733242034912</v>
+        <v>0.6890734434127808</v>
       </c>
       <c r="F2" s="1">
-        <v>0.09578119206428549</v>
+        <v>0.09578120863437674</v>
       </c>
       <c r="G2" s="1">
-        <v>0.04522043690085413</v>
+        <v>0.04522044472396376</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.02584024965763094</v>
+        <v>0.0258402541279793</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.06089685502648356</v>
+        <v>0.06089686556160453</v>
       </c>
       <c r="L2" s="1">
-        <v>0.03979398447275164</v>
+        <v>0.03979399135708812</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -25571,10 +25571,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0.08802911716699621</v>
+        <v>0.08802913239598295</v>
       </c>
       <c r="P2" s="1">
-        <v>0.03876037448644638</v>
+        <v>0.03876038119196892</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -25586,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="1">
-        <v>0.07769301730394365</v>
+        <v>0.07769303074479104</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
@@ -25595,7 +25595,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.5279847729206085</v>
+        <v>0.5279846912622452</v>
       </c>
     </row>
     <row r="3">
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205444138646</v>
+        <v>0.581220639074136</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953401823087432</v>
+        <v>0.0995340344414458</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972592154389034</v>
+        <v>0.08972593615706974</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179577041551994</v>
+        <v>0.02179577396528012</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563143269114</v>
+        <v>0.1220563342055684</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010972816992242</v>
+        <v>0.07010973958831766</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525703929086396</v>
+        <v>0.01525704177569609</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230984899724782</v>
+        <v>0.05230985751667225</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365562327989</v>
+        <v>0.03269366094792015</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248120852449047</v>
+        <v>0.06248121870046965</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525703929086396</v>
+        <v>0.01525704177569609</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187794555861354</v>
+        <v>0.418779360925864</v>
       </c>
     </row>
     <row r="7">
@@ -30824,19 +30824,19 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890733242034912</v>
+        <v>0.6890734434127808</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2675327181220057</v>
+        <v>0.2675327644050124</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03876037448644638</v>
+        <v>0.03876038119196892</v>
       </c>
       <c r="H2" s="1">
-        <v>0.1657221344709399</v>
+        <v>0.165722163140774</v>
       </c>
       <c r="I2" s="1">
-        <v>0.5279847729206085</v>
+        <v>0.5279846912622452</v>
       </c>
     </row>
     <row r="3">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205444138646</v>
+        <v>0.581220639074136</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184787919779824</v>
+        <v>0.4184788601333778</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795069491414385</v>
+        <v>0.04795070272361624</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910575217383</v>
+        <v>0.1147910762171419</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187794555861354</v>
+        <v>0.418779360925864</v>
       </c>
     </row>
     <row r="7">
@@ -33402,25 +33402,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.1173905960321429</v>
+        <v>0.1173906043171885</v>
       </c>
       <c r="E2" s="1">
-        <v>0.05542271845042708</v>
+        <v>0.0554227223619819</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03167012482881549</v>
+        <v>0.03167012706398967</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0746359275132418</v>
+        <v>0.07463593278080229</v>
       </c>
       <c r="J2" s="1">
-        <v>0.04877199223637584</v>
+        <v>0.04877199567854408</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1078895585834983</v>
+        <v>0.1078895661979916</v>
       </c>
       <c r="N2" s="1">
-        <v>0.0475051872432232</v>
+        <v>0.04750519059598446</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -33444,7 +33444,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>0.09522150865197183</v>
+        <v>0.09522151537239554</v>
       </c>
       <c r="S2" s="1">
         <v>0</v>
@@ -33453,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4214923864603043</v>
+        <v>0.4214923456311226</v>
       </c>
     </row>
     <row r="3">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920091154372</v>
+        <v>0.1353920172207229</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504607719452</v>
+        <v>0.1220504680785349</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788520775999</v>
+        <v>0.02964788698264008</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281571634556</v>
+        <v>0.1660281671027841</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736408496121</v>
+        <v>0.09536736979415883</v>
       </c>
       <c r="J6" s="1">
-        <v>0.020753519645432</v>
+        <v>0.02075352088784806</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492449862391</v>
+        <v>0.07115492875833612</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182781163994</v>
+        <v>0.04447183047396008</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060426224525</v>
+        <v>0.08499060935023484</v>
       </c>
       <c r="S6" s="1">
-        <v>0.020753519645432</v>
+        <v>0.02075352088784806</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897277930677</v>
+        <v>0.209389680462932</v>
       </c>
     </row>
     <row r="7">
@@ -38145,16 +38145,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3278913590610031</v>
+        <v>0.3278913822025065</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0475051872432232</v>
+        <v>0.04750519059598446</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2031110672354701</v>
+        <v>0.2031110815703872</v>
       </c>
       <c r="G2" s="1">
-        <v>0.4214923864603043</v>
+        <v>0.4214923456311226</v>
       </c>
     </row>
     <row r="3">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692393959889912</v>
+        <v>0.5692394300666889</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522534745707194</v>
+        <v>0.06522535136180814</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455287608692</v>
+        <v>0.156145538108571</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897277930677</v>
+        <v>0.209389680462932</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -226,7 +226,7 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.1390000000000003</v>
+        <v>0.1075</v>
       </c>
       <c r="E2" s="1">
         <v>0.06562500000000003</v>
@@ -265,13 +265,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
-        <v>0</v>
+        <v>0.03150000000000001</v>
       </c>
       <c r="R2" s="1">
-        <v>0.11275</v>
+        <v>0.08125</v>
       </c>
       <c r="S2" s="1">
-        <v>0</v>
+        <v>0.03150000000000001</v>
       </c>
       <c r="T2" s="1">
         <v>0</v>
@@ -18104,10 +18104,10 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3882500000000004</v>
+        <v>0.3567500000000002</v>
       </c>
       <c r="E2" s="1">
-        <v>0.05625</v>
+        <v>0.08775000000000001</v>
       </c>
       <c r="F2" s="1">
         <v>0.2405000000000003</v>
@@ -25541,28 +25541,28 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890734434127808</v>
+        <v>0.7104738354682922</v>
       </c>
       <c r="F2" s="1">
-        <v>0.09578120863437674</v>
+        <v>0.07637593731284144</v>
       </c>
       <c r="G2" s="1">
-        <v>0.04522044472396376</v>
+        <v>0.0466248454526067</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0258402541279793</v>
+        <v>0.02664276883006098</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.06089686556160453</v>
+        <v>0.06278812520951035</v>
       </c>
       <c r="L2" s="1">
-        <v>0.03979399135708812</v>
+        <v>0.04102986399829391</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -25571,10 +25571,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0.08802913239598295</v>
+        <v>0.09076303248107455</v>
       </c>
       <c r="P2" s="1">
-        <v>0.03876038119196892</v>
+        <v>0.03996415324509144</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -25583,19 +25583,19 @@
         <v>0</v>
       </c>
       <c r="S2" s="1">
-        <v>0</v>
+        <v>0.02237992581725121</v>
       </c>
       <c r="T2" s="1">
-        <v>0.07769303074479104</v>
+        <v>0.05772599913179875</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
+        <v>0.02237992581725121</v>
       </c>
       <c r="V2" s="1">
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.5279846912622452</v>
+        <v>0.5133254227042199</v>
       </c>
     </row>
     <row r="3">
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.581220639074136</v>
+        <v>0.5812205231885413</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0995340344414458</v>
+        <v>0.09953401459603771</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972593615706974</v>
+        <v>0.08972591826723106</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179577396528012</v>
+        <v>0.02179576961957032</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563342055684</v>
+        <v>0.1220563098695935</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010973958831766</v>
+        <v>0.0701097256096178</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525704177569609</v>
+        <v>0.01525703873369923</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230985751667225</v>
+        <v>0.05230984708696872</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269366094792015</v>
+        <v>0.03269365442935545</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248121870046965</v>
+        <v>0.06248120624276822</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525704177569609</v>
+        <v>0.01525703873369923</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.418779360925864</v>
+        <v>0.4187794768114587</v>
       </c>
     </row>
     <row r="7">
@@ -30824,19 +30824,19 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.6890734434127808</v>
+        <v>0.7104738354682922</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2675327644050124</v>
+        <v>0.2534615408033134</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03876038119196892</v>
+        <v>0.06234407906234266</v>
       </c>
       <c r="H2" s="1">
-        <v>0.165722163140774</v>
+        <v>0.1708689574301245</v>
       </c>
       <c r="I2" s="1">
-        <v>0.5279846912622452</v>
+        <v>0.5133254227042199</v>
       </c>
     </row>
     <row r="3">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.581220639074136</v>
+        <v>0.5812205231885413</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184788601333778</v>
+        <v>0.4184787766957496</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795070272361624</v>
+        <v>0.04795069316305468</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910762171419</v>
+        <v>0.1147910533297369</v>
       </c>
       <c r="I6" s="1">
-        <v>0.418779360925864</v>
+        <v>0.4187794768114587</v>
       </c>
     </row>
     <row r="7">
@@ -33402,25 +33402,25 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.1173906043171885</v>
+        <v>0.09193796865642073</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0554227223619819</v>
+        <v>0.05612492272630337</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03167012706398967</v>
+        <v>0.0320713844150305</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.07463593278080229</v>
+        <v>0.0755815626047552</v>
       </c>
       <c r="J2" s="1">
-        <v>0.04877199567854408</v>
+        <v>0.04938993199914697</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1078895661979916</v>
+        <v>0.1092565162405374</v>
       </c>
       <c r="N2" s="1">
-        <v>0.04750519059598446</v>
+        <v>0.04810707662254572</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
@@ -33441,19 +33441,19 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
-        <v>0</v>
+        <v>0.02693996290862561</v>
       </c>
       <c r="R2" s="1">
-        <v>0.09522151537239554</v>
+        <v>0.06948799956589938</v>
       </c>
       <c r="S2" s="1">
-        <v>0</v>
+        <v>0.02693996290862561</v>
       </c>
       <c r="T2" s="1">
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4214923456311226</v>
+        <v>0.4141627113521099</v>
       </c>
     </row>
     <row r="3">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920172207229</v>
+        <v>0.1353920072980189</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504680785349</v>
+        <v>0.1220504591336155</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788698264008</v>
+        <v>0.02964788480978518</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281671027841</v>
+        <v>0.1660281549347966</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736979415883</v>
+        <v>0.0953673628048089</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075352088784806</v>
+        <v>0.02075351936684963</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492875833612</v>
+        <v>0.07115492354348436</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447183047396008</v>
+        <v>0.04447182721467773</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060935023484</v>
+        <v>0.08499060312138412</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075352088784806</v>
+        <v>0.02075351936684963</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.209389680462932</v>
+        <v>0.2093897384057293</v>
       </c>
     </row>
     <row r="7">
@@ -38145,16 +38145,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3278913822025065</v>
+        <v>0.3051057704016568</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04750519059598446</v>
+        <v>0.07504703953117134</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2031110815703872</v>
+        <v>0.2056844787150624</v>
       </c>
       <c r="G2" s="1">
-        <v>0.4214923456311226</v>
+        <v>0.4141627113521099</v>
       </c>
     </row>
     <row r="3">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692394300666889</v>
+        <v>0.5692393883478747</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522535136180814</v>
+        <v>0.06522534658152736</v>
       </c>
       <c r="F6" s="1">
-        <v>0.156145538108571</v>
+        <v>0.1561455266648685</v>
       </c>
       <c r="G6" s="1">
-        <v>0.209389680462932</v>
+        <v>0.2093897384057293</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25422,7 +25422,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREVIEW</t>
+          <t xml:space="preserve">OFFICIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -25441,28 +25441,28 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.730446457862854</v>
+        <v>0.7122377157211304</v>
       </c>
       <c r="F2" s="1">
-        <v>0.07852299422025684</v>
+        <v>0.09526179447770097</v>
       </c>
       <c r="G2" s="1">
-        <v>0.04793554879724982</v>
+        <v>0.0467406000941992</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.02739174216985705</v>
+        <v>0.02670891433954241</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.07030547156929971</v>
+        <v>0.05920476011931895</v>
       </c>
       <c r="L2" s="1">
-        <v>0.04793554879724982</v>
+        <v>0.03739248007535932</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>0.09906680084764979</v>
+        <v>0.06944317728281001</v>
       </c>
       <c r="P2" s="1">
-        <v>0.04108761325478554</v>
+        <v>0.04006337150931358</v>
       </c>
       <c r="Q2" s="1">
         <v>0</v>
@@ -25483,10 +25483,10 @@
         <v>0</v>
       </c>
       <c r="S2" s="1">
-        <v>0.02876132927834988</v>
+        <v>0.01780594289302826</v>
       </c>
       <c r="T2" s="1">
-        <v>0.05934877470135689</v>
+        <v>0.05786931440234185</v>
       </c>
       <c r="U2" s="1">
         <v>0</v>
@@ -25495,7 +25495,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.499644176363945</v>
+        <v>0.5495096448063848</v>
       </c>
     </row>
     <row r="3">
@@ -25757,28 +25757,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812204769124886</v>
+        <v>0.5812205304998401</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953400667126368</v>
+        <v>0.09953401584809762</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972591112336542</v>
+        <v>0.0897259193959128</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179576788421834</v>
+        <v>0.02179576989374402</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563001516224</v>
+        <v>0.1220563114049663</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010972002756893</v>
+        <v>0.07010972649154322</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525703751895284</v>
+        <v>0.01525703892562082</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25787,10 +25787,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230984292212398</v>
+        <v>0.05230984774498561</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365182632748</v>
+        <v>0.03269365484061601</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25802,16 +25802,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248120126809254</v>
+        <v>0.06248120702873284</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525703751895284</v>
+        <v>0.01525703892562082</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187795230875114</v>
+        <v>0.4187794695001599</v>
       </c>
     </row>
     <row r="7">
@@ -30705,7 +30705,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREVIEW</t>
+          <t xml:space="preserve">OFFICIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -30724,19 +30724,19 @@
         </is>
       </c>
       <c r="E2" s="1">
-        <v>0.730446457862854</v>
+        <v>0.7122377157211304</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2720913055539132</v>
+        <v>0.2653085491061208</v>
       </c>
       <c r="G2" s="1">
-        <v>0.04108761325478554</v>
+        <v>0.04006337150931358</v>
       </c>
       <c r="H2" s="1">
-        <v>0.1871769048273565</v>
+        <v>0.1451184345781801</v>
       </c>
       <c r="I2" s="1">
-        <v>0.499644176363945</v>
+        <v>0.5495096448063848</v>
       </c>
     </row>
     <row r="3">
@@ -30872,19 +30872,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812204769124886</v>
+        <v>0.5812205304998401</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184787433769916</v>
+        <v>0.4184787819598847</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795068934528032</v>
+        <v>0.04795069376623683</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910441902165</v>
+        <v>0.1147910547737185</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187795230875114</v>
+        <v>0.4187794695001599</v>
       </c>
     </row>
     <row r="7">
@@ -33515,25 +33515,25 @@
         </is>
       </c>
       <c r="D5" s="1">
-        <v>0.1353920033356318</v>
+        <v>0.1353920079240488</v>
       </c>
       <c r="E5" s="1">
-        <v>0.1220504555616827</v>
+        <v>0.1220504596979564</v>
       </c>
       <c r="F5" s="1">
-        <v>0.02964788394210919</v>
+        <v>0.02964788494687203</v>
       </c>
       <c r="G5" s="1">
-        <v>0.1660281500758111</v>
+        <v>0.166028155702483</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0.09536736001378447</v>
+        <v>0.09536736324577161</v>
       </c>
       <c r="J5" s="1">
-        <v>0.02075351875947644</v>
+        <v>0.02075351946281043</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>0.07115492146106199</v>
+        <v>0.07115492387249281</v>
       </c>
       <c r="N5" s="1">
-        <v>0.04447182591316375</v>
+        <v>0.044471827420308</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -33557,16 +33557,16 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>0.08499060063404629</v>
+        <v>0.08499060351436644</v>
       </c>
       <c r="S5" s="1">
-        <v>0.02075351875947644</v>
+        <v>0.02075351946281043</v>
       </c>
       <c r="T5" s="1">
         <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>0.2093897615437557</v>
+        <v>0.2093897347500799</v>
       </c>
     </row>
     <row r="6">
@@ -38061,16 +38061,16 @@
         </is>
       </c>
       <c r="D5" s="1">
-        <v>0.5692393716884957</v>
+        <v>0.5692393909799423</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06522534467264018</v>
+        <v>0.06522534688311843</v>
       </c>
       <c r="F5" s="1">
-        <v>0.1561455220951083</v>
+        <v>0.1561455273868592</v>
       </c>
       <c r="G5" s="1">
-        <v>0.2093897615437557</v>
+        <v>0.2093897347500799</v>
       </c>
     </row>
     <row r="6">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25757,28 +25757,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205304998401</v>
+        <v>0.5812205077585513</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953401584809762</v>
+        <v>0.09953401195365191</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0897259193959128</v>
+        <v>0.08972591588522634</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179576989374402</v>
+        <v>0.02179576904094569</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563114049663</v>
+        <v>0.1220563066292956</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010972649154322</v>
+        <v>0.07010972374837525</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525703892562082</v>
+        <v>0.01525703832866199</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25787,10 +25787,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230984774498561</v>
+        <v>0.05230984569826962</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365484061601</v>
+        <v>0.03269365356141851</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25802,16 +25802,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248120702873284</v>
+        <v>0.06248120458404428</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525703892562082</v>
+        <v>0.01525703832866199</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187794695001599</v>
+        <v>0.4187794922414487</v>
       </c>
     </row>
     <row r="7">
@@ -30872,19 +30872,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205304998401</v>
+        <v>0.5812205077585513</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184787819598847</v>
+        <v>0.4184787655861568</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795069376623683</v>
+        <v>0.0479506918900805</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910547737185</v>
+        <v>0.1147910502823139</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187794695001599</v>
+        <v>0.4187794922414487</v>
       </c>
     </row>
     <row r="7">
@@ -33515,25 +33515,25 @@
         </is>
       </c>
       <c r="D5" s="1">
-        <v>0.1353920079240488</v>
+        <v>0.135392005976826</v>
       </c>
       <c r="E5" s="1">
-        <v>0.1220504596979564</v>
+        <v>0.1220504579426132</v>
       </c>
       <c r="F5" s="1">
-        <v>0.02964788494687203</v>
+        <v>0.02964788452047286</v>
       </c>
       <c r="G5" s="1">
-        <v>0.166028155702483</v>
+        <v>0.1660281533146477</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0.09536736324577161</v>
+        <v>0.09536736187418762</v>
       </c>
       <c r="J5" s="1">
-        <v>0.02075351946281043</v>
+        <v>0.02075351916433101</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -33542,10 +33542,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>0.07115492387249281</v>
+        <v>0.07115492284913481</v>
       </c>
       <c r="N5" s="1">
-        <v>0.044471827420308</v>
+        <v>0.04447182678070925</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -33557,16 +33557,16 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>0.08499060351436644</v>
+        <v>0.08499060229202215</v>
       </c>
       <c r="S5" s="1">
-        <v>0.02075351946281043</v>
+        <v>0.02075351916433101</v>
       </c>
       <c r="T5" s="1">
         <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>0.2093897347500799</v>
+        <v>0.2093897461207244</v>
       </c>
     </row>
     <row r="6">
@@ -38061,16 +38061,16 @@
         </is>
       </c>
       <c r="D5" s="1">
-        <v>0.5692393909799423</v>
+        <v>0.5692393827930783</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06522534688311843</v>
+        <v>0.06522534594504026</v>
       </c>
       <c r="F5" s="1">
-        <v>0.1561455273868592</v>
+        <v>0.156145525141157</v>
       </c>
       <c r="G5" s="1">
-        <v>0.2093897347500799</v>
+        <v>0.2093897461207244</v>
       </c>
     </row>
     <row r="6">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205781464601</v>
+        <v>0.5812205841434082</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0995340240075813</v>
+        <v>0.09953402503455866</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972592675135976</v>
+        <v>0.08972592767713862</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179577168049227</v>
+        <v>0.02179577190537783</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563214107565</v>
+        <v>0.1220563226701155</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010973223891676</v>
+        <v>0.07010973296229861</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525704017634459</v>
+        <v>0.01525704033376448</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230985203318141</v>
+        <v>0.05230985257290674</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365752073838</v>
+        <v>0.03269365785806671</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248121215074449</v>
+        <v>0.0624812127954164</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525704017634459</v>
+        <v>0.01525704033376448</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187794218535399</v>
+        <v>0.4187794158565918</v>
       </c>
     </row>
     <row r="7">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205781464601</v>
+        <v>0.5812205841434082</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184788162654511</v>
+        <v>0.4184788205832537</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795069769708298</v>
+        <v>0.04795069819183119</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910641839259</v>
+        <v>0.1147910653683231</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187794218535399</v>
+        <v>0.4187794158565918</v>
       </c>
     </row>
     <row r="7">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920120037906</v>
+        <v>0.1353920125172793</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504633756799</v>
+        <v>0.1220504638385693</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788584024615</v>
+        <v>0.02964788595268893</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281607053781</v>
+        <v>0.1660281613350576</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736611945838</v>
+        <v>0.09536736648114931</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075352008817231</v>
+        <v>0.02075352016688226</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492601659071</v>
+        <v>0.07115492628645337</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182876036919</v>
+        <v>0.04447182892903336</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060607537226</v>
+        <v>0.08499060639770822</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075352008817231</v>
+        <v>0.02075352016688226</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897109267699</v>
+        <v>0.2093897079282959</v>
       </c>
     </row>
     <row r="7">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692394081327254</v>
+        <v>0.5692394102916267</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0652253488485415</v>
+        <v>0.06522534909591561</v>
       </c>
       <c r="F6" s="1">
-        <v>0.156145532091963</v>
+        <v>0.1561455326841616</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897109267699</v>
+        <v>0.2093897079282959</v>
       </c>
     </row>
     <row r="7">
@@ -40101,7 +40101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005-11 to 2026-08</t>
+          <t xml:space="preserve">2005-11 to 2026-09</t>
         </is>
       </c>
     </row>

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205841434082</v>
+        <v>0.5812204842204874</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953402503455866</v>
+        <v>0.09953400792275849</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972592767713862</v>
+        <v>0.08972591225153774</v>
       </c>
       <c r="H6" s="1">
-        <v>0.02179577190537783</v>
+        <v>0.0217957681582683</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563226701155</v>
+        <v>0.1220563016863022</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.07010973296229861</v>
+        <v>0.0701097209090963</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525704033376448</v>
+        <v>0.01525703771078781</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230985257290674</v>
+        <v>0.05230984357984388</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365785806671</v>
+        <v>0.03269365223740242</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.0624812127954164</v>
+        <v>0.06248120205370242</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525704033376448</v>
+        <v>0.01525703771078781</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187794158565918</v>
+        <v>0.4187795157795126</v>
       </c>
     </row>
     <row r="7">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812205841434082</v>
+        <v>0.5812204842204874</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184788205832537</v>
+        <v>0.4184787486387508</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795069819183119</v>
+        <v>0.04795068994819023</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910653683231</v>
+        <v>0.1147910456335463</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187794158565918</v>
+        <v>0.4187795157795126</v>
       </c>
     </row>
     <row r="7">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920125172793</v>
+        <v>0.1353920039613792</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504638385693</v>
+        <v>0.1220504561257689</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788595268893</v>
+        <v>0.02964788407913416</v>
       </c>
       <c r="G6" s="1">
-        <v>0.1660281613350576</v>
+        <v>0.166028150843151</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736648114931</v>
+        <v>0.09536736045454816</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075352016688226</v>
+        <v>0.02075351885539392</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492628645337</v>
+        <v>0.07115492178992194</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182892903336</v>
+        <v>0.04447182611870121</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060639770822</v>
+        <v>0.08499060102685123</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075352016688226</v>
+        <v>0.02075351885539392</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897079282959</v>
+        <v>0.2093897578897563</v>
       </c>
     </row>
     <row r="7">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692394102916267</v>
+        <v>0.5692393743193753</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522534909591561</v>
+        <v>0.06522534497409513</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455326841616</v>
+        <v>0.1561455228167732</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897079282959</v>
+        <v>0.2093897578897563</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -25857,28 +25857,28 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812204842204874</v>
+        <v>0.5812206675271373</v>
       </c>
       <c r="F6" s="1">
-        <v>0.09953400792275849</v>
+        <v>0.09953403931402227</v>
       </c>
       <c r="G6" s="1">
-        <v>0.08972591225153774</v>
+        <v>0.08972594054950181</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0217957681582683</v>
+        <v>0.02179577503226767</v>
       </c>
       <c r="I6" s="1">
-        <v>0.1220563016863022</v>
+        <v>0.1220563401806987</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.0701097209090963</v>
+        <v>0.07010974302046094</v>
       </c>
       <c r="L6" s="1">
-        <v>0.01525703771078781</v>
+        <v>0.01525704252258737</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
@@ -25887,10 +25887,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0.05230984357984388</v>
+        <v>0.05230986007744236</v>
       </c>
       <c r="P6" s="1">
-        <v>0.03269365223740242</v>
+        <v>0.03269366254840148</v>
       </c>
       <c r="Q6" s="1">
         <v>0</v>
@@ -25902,16 +25902,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06248120205370242</v>
+        <v>0.06248122175916728</v>
       </c>
       <c r="U6" s="1">
-        <v>0.01525703771078781</v>
+        <v>0.01525704252258737</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
-        <v>0.4187795157795126</v>
+        <v>0.4187793324728627</v>
       </c>
     </row>
     <row r="7">
@@ -30972,19 +30972,19 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <v>0.5812204842204874</v>
+        <v>0.5812206675271373</v>
       </c>
       <c r="F6" s="1">
-        <v>0.4184787486387508</v>
+        <v>0.4184788806195387</v>
       </c>
       <c r="G6" s="1">
-        <v>0.04795068994819023</v>
+        <v>0.04795070507098885</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1147910456335463</v>
+        <v>0.1147910818366096</v>
       </c>
       <c r="I6" s="1">
-        <v>0.4187795157795126</v>
+        <v>0.4187793324728627</v>
       </c>
     </row>
     <row r="7">
@@ -33686,25 +33686,25 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.1353920039613792</v>
+        <v>0.1353920196570111</v>
       </c>
       <c r="E6" s="1">
-        <v>0.1220504561257689</v>
+        <v>0.1220504702747509</v>
       </c>
       <c r="F6" s="1">
-        <v>0.02964788407913416</v>
+        <v>0.02964788751613385</v>
       </c>
       <c r="G6" s="1">
-        <v>0.166028150843151</v>
+        <v>0.1660281700903492</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.09536736045454816</v>
+        <v>0.09536737151023048</v>
       </c>
       <c r="J6" s="1">
-        <v>0.02075351885539392</v>
+        <v>0.0207535212612937</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -33713,10 +33713,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0.07115492178992194</v>
+        <v>0.07115493003872118</v>
       </c>
       <c r="N6" s="1">
-        <v>0.04447182611870121</v>
+        <v>0.04447183127420073</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -33728,16 +33728,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0.08499060102685123</v>
+        <v>0.08499061087958366</v>
       </c>
       <c r="S6" s="1">
-        <v>0.02075351885539392</v>
+        <v>0.0207535212612937</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0.2093897578897563</v>
+        <v>0.2093896662364313</v>
       </c>
     </row>
     <row r="7">
@@ -38261,16 +38261,16 @@
         </is>
       </c>
       <c r="D6" s="1">
-        <v>0.5692393743193753</v>
+        <v>0.5692394403097693</v>
       </c>
       <c r="E6" s="1">
-        <v>0.06522534497409513</v>
+        <v>0.06522535253549444</v>
       </c>
       <c r="F6" s="1">
-        <v>0.1561455228167732</v>
+        <v>0.1561455409183048</v>
       </c>
       <c r="G6" s="1">
-        <v>0.2093897578897563</v>
+        <v>0.2093896662364313</v>
       </c>
     </row>
     <row r="7">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -229,10 +229,10 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="E2" s="1">
-        <v>0.06562500000000003</v>
+        <v>0.09187499999999971</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G2" s="1">
         <v>0.03750000000000003</v>
@@ -265,7 +265,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1">
         <v>0.05625</v>
@@ -277,7 +277,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -18175,16 +18175,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3462499999999998</v>
+        <v>0.3974999999999995</v>
       </c>
       <c r="E2" s="1">
         <v>0.05625</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2037499999999997</v>
+        <v>0.1787499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -25647,10 +25647,10 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.06562500000000003</v>
+        <v>0.09187499999999971</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I2" s="1">
         <v>0.03750000000000003</v>
@@ -25683,7 +25683,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T2" s="1">
         <v>0.05625</v>
@@ -25695,7 +25695,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -26036,28 +26036,28 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205392093202</v>
+        <v>0.5812205928018681</v>
       </c>
       <c r="F7" s="1">
-        <v>0.09953401733959609</v>
+        <v>0.09953402651731992</v>
       </c>
       <c r="G7" s="1">
-        <v>0.08972592074043879</v>
+        <v>0.08972592901378838</v>
       </c>
       <c r="H7" s="1">
-        <v>0.02179577022034953</v>
+        <v>0.02179577223007007</v>
       </c>
       <c r="I7" s="1">
-        <v>0.1220563132339571</v>
+        <v>0.1220563244883921</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.07010972754212424</v>
+        <v>0.07010973400672535</v>
       </c>
       <c r="L7" s="1">
-        <v>0.01525703915424467</v>
+        <v>0.01525704056104906</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0.05230984852883882</v>
+        <v>0.05230985335216814</v>
       </c>
       <c r="P7" s="1">
-        <v>0.03269365533052426</v>
+        <v>0.03269365834510508</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -26081,16 +26081,16 @@
         <v>0</v>
       </c>
       <c r="T7" s="1">
-        <v>0.06248120796500194</v>
+        <v>0.06248121372620084</v>
       </c>
       <c r="U7" s="1">
-        <v>0.01525703915424467</v>
+        <v>0.01525704056104906</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
       <c r="W7" s="1">
-        <v>0.4187794607906798</v>
+        <v>0.4187794071981319</v>
       </c>
     </row>
     <row r="8">
@@ -31006,16 +31006,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>0.3462499999999998</v>
+        <v>0.3974999999999995</v>
       </c>
       <c r="G2" s="1">
         <v>0.05625</v>
       </c>
       <c r="H2" s="1">
-        <v>0.2037499999999997</v>
+        <v>0.1787499999999997</v>
       </c>
       <c r="I2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -31188,19 +31188,19 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205392093202</v>
+        <v>0.5812205928018681</v>
       </c>
       <c r="F7" s="1">
-        <v>0.4184787882307104</v>
+        <v>0.4184788268173449</v>
       </c>
       <c r="G7" s="1">
-        <v>0.04795069448476894</v>
+        <v>0.04795069890615414</v>
       </c>
       <c r="H7" s="1">
-        <v>0.1147910564938407</v>
+        <v>0.114791067078369</v>
       </c>
       <c r="I7" s="1">
-        <v>0.4187794607906798</v>
+        <v>0.4187794071981319</v>
       </c>
     </row>
     <row r="8">
@@ -33621,10 +33621,10 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="E2" s="1">
-        <v>0.06562500000000003</v>
+        <v>0.09187499999999971</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G2" s="1">
         <v>0.03750000000000003</v>
@@ -33657,7 +33657,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1">
         <v>0.05625</v>
@@ -33669,7 +33669,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -33973,25 +33973,25 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.1353920086697981</v>
+        <v>0.13539201325866</v>
       </c>
       <c r="E7" s="1">
-        <v>0.1220504603702194</v>
+        <v>0.1220504645068942</v>
       </c>
       <c r="F7" s="1">
-        <v>0.02964788511017478</v>
+        <v>0.02964788611503505</v>
       </c>
       <c r="G7" s="1">
-        <v>0.1660281566169784</v>
+        <v>0.1660281622441959</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.09536736377106213</v>
+        <v>0.09536736700336268</v>
       </c>
       <c r="J7" s="1">
-        <v>0.02075351957712235</v>
+        <v>0.02075352028052454</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -34000,10 +34000,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0.07115492426441941</v>
+        <v>0.07115492667608407</v>
       </c>
       <c r="N7" s="1">
-        <v>0.04447182766526213</v>
+        <v>0.04447182917255255</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -34015,16 +34015,16 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>0.084990603982501</v>
+        <v>0.08499060686310045</v>
       </c>
       <c r="S7" s="1">
-        <v>0.02075351957712235</v>
+        <v>0.02075352028052454</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="U7" s="1">
-        <v>0.2093897303953399</v>
+        <v>0.2093897035990659</v>
       </c>
     </row>
     <row r="8">
@@ -38432,16 +38432,16 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3462499999999998</v>
+        <v>0.3974999999999995</v>
       </c>
       <c r="E2" s="1">
         <v>0.05625</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2037499999999997</v>
+        <v>0.1787499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.39375</v>
+        <v>0.3674999999999997</v>
       </c>
     </row>
     <row r="3">
@@ -38577,16 +38577,16 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.5692393941153551</v>
+        <v>0.5692394134086723</v>
       </c>
       <c r="E7" s="1">
-        <v>0.06522534724238448</v>
+        <v>0.06522534945307709</v>
       </c>
       <c r="F7" s="1">
-        <v>0.1561455282469204</v>
+        <v>0.1561455335391845</v>
       </c>
       <c r="G7" s="1">
-        <v>0.2093897303953399</v>
+        <v>0.2093897035990659</v>
       </c>
     </row>
     <row r="8">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -26036,28 +26036,28 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205928018681</v>
+        <v>0.5812205042632564</v>
       </c>
       <c r="F7" s="1">
-        <v>0.09953402651731992</v>
+        <v>0.09953401135508268</v>
       </c>
       <c r="G7" s="1">
-        <v>0.08972592901378838</v>
+        <v>0.0897259153456402</v>
       </c>
       <c r="H7" s="1">
-        <v>0.02179577223007007</v>
+        <v>0.02179576890987214</v>
       </c>
       <c r="I7" s="1">
-        <v>0.1220563244883921</v>
+        <v>0.1220563058952837</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.07010973400672535</v>
+        <v>0.07010972332675532</v>
       </c>
       <c r="L7" s="1">
-        <v>0.01525704056104906</v>
+        <v>0.0152570382369105</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0.05230985335216814</v>
+        <v>0.05230984538369308</v>
       </c>
       <c r="P7" s="1">
-        <v>0.03269365834510508</v>
+        <v>0.03269365336480817</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -26081,16 +26081,16 @@
         <v>0</v>
       </c>
       <c r="T7" s="1">
-        <v>0.06248121372620084</v>
+        <v>0.06248120420830009</v>
       </c>
       <c r="U7" s="1">
-        <v>0.01525704056104906</v>
+        <v>0.0152570382369105</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
       <c r="W7" s="1">
-        <v>0.4187794071981319</v>
+        <v>0.4187794957367436</v>
       </c>
     </row>
     <row r="8">
@@ -31188,19 +31188,19 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205928018681</v>
+        <v>0.5812205042632564</v>
       </c>
       <c r="F7" s="1">
-        <v>0.4184788268173449</v>
+        <v>0.4184787630695445</v>
       </c>
       <c r="G7" s="1">
-        <v>0.04795069890615414</v>
+        <v>0.04795069160171867</v>
       </c>
       <c r="H7" s="1">
-        <v>0.114791067078369</v>
+        <v>0.1147910495919932</v>
       </c>
       <c r="I7" s="1">
-        <v>0.4187794071981319</v>
+        <v>0.4187794957367436</v>
       </c>
     </row>
     <row r="8">
@@ -33973,25 +33973,25 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.13539201325866</v>
+        <v>0.1353920056775413</v>
       </c>
       <c r="E7" s="1">
-        <v>0.1220504645068942</v>
+        <v>0.1220504576728201</v>
       </c>
       <c r="F7" s="1">
-        <v>0.02964788611503505</v>
+        <v>0.02964788445493608</v>
       </c>
       <c r="G7" s="1">
-        <v>0.1660281622441959</v>
+        <v>0.1660281529476417</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.09536736700336268</v>
+        <v>0.09536736166337767</v>
       </c>
       <c r="J7" s="1">
-        <v>0.02075352028052454</v>
+        <v>0.02075351911845526</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -34000,10 +34000,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0.07115492667608407</v>
+        <v>0.07115492269184655</v>
       </c>
       <c r="N7" s="1">
-        <v>0.04447182917255255</v>
+        <v>0.04447182668240408</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -34015,16 +34015,16 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>0.08499060686310045</v>
+        <v>0.08499060210415006</v>
       </c>
       <c r="S7" s="1">
-        <v>0.02075352028052454</v>
+        <v>0.02075351911845526</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="U7" s="1">
-        <v>0.2093897035990659</v>
+        <v>0.2093897478683718</v>
       </c>
     </row>
     <row r="8">
@@ -38577,16 +38577,16 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.5692394134086723</v>
+        <v>0.5692393815347722</v>
       </c>
       <c r="E7" s="1">
-        <v>0.06522534945307709</v>
+        <v>0.06522534580085934</v>
       </c>
       <c r="F7" s="1">
-        <v>0.1561455335391845</v>
+        <v>0.1561455247959966</v>
       </c>
       <c r="G7" s="1">
-        <v>0.2093897035990659</v>
+        <v>0.2093897478683718</v>
       </c>
     </row>
     <row r="8">

--- a/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
+++ b/public/assets/systems/pds/PDS_Portfolio_History_Current_Definition.xlsx
@@ -229,19 +229,19 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="E2" s="1">
-        <v>0.09187499999999971</v>
+        <v>0.1168749999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03750000000000003</v>
+        <v>0.01125</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.08312499999999998</v>
+        <v>0.030625</v>
       </c>
       <c r="J2" s="1">
         <v>0.02625000000000003</v>
@@ -277,7 +277,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3974999999999995</v>
+        <v>0.3187499999999995</v>
       </c>
       <c r="E2" s="1">
         <v>0.05625</v>
@@ -18184,7 +18184,7 @@
         <v>0.1787499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -25647,19 +25647,19 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.09187499999999971</v>
+        <v>0.1168749999999997</v>
       </c>
       <c r="H2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.03750000000000003</v>
+        <v>0.01125</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.08312499999999998</v>
+        <v>0.030625</v>
       </c>
       <c r="L2" s="1">
         <v>0.02625000000000003</v>
@@ -25695,7 +25695,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -26036,28 +26036,28 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205042632564</v>
+        <v>0.5812204586440203</v>
       </c>
       <c r="F7" s="1">
-        <v>0.09953401135508268</v>
+        <v>0.09953400354278848</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0897259153456402</v>
+        <v>0.08972590830317062</v>
       </c>
       <c r="H7" s="1">
-        <v>0.02179576890987214</v>
+        <v>0.02179576719915078</v>
       </c>
       <c r="I7" s="1">
-        <v>0.1220563058952837</v>
+        <v>0.1220562963152441</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.07010972332675532</v>
+        <v>0.07010971782393495</v>
       </c>
       <c r="L7" s="1">
-        <v>0.0152570382369105</v>
+        <v>0.01525703703940555</v>
       </c>
       <c r="M7" s="1">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0.05230984538369308</v>
+        <v>0.05230984127796183</v>
       </c>
       <c r="P7" s="1">
-        <v>0.03269365336480817</v>
+        <v>0.03269365079872614</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -26081,16 +26081,16 @@
         <v>0</v>
       </c>
       <c r="T7" s="1">
-        <v>0.06248120420830009</v>
+        <v>0.0624811993042322</v>
       </c>
       <c r="U7" s="1">
-        <v>0.0152570382369105</v>
+        <v>0.01525703703940555</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
       <c r="W7" s="1">
-        <v>0.4187794957367436</v>
+        <v>0.4187795413559797</v>
       </c>
     </row>
     <row r="8">
@@ -31006,7 +31006,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>0.3974999999999995</v>
+        <v>0.3187499999999995</v>
       </c>
       <c r="G2" s="1">
         <v>0.05625</v>
@@ -31015,7 +31015,7 @@
         <v>0.1787499999999997</v>
       </c>
       <c r="I2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -31188,19 +31188,19 @@
         </is>
       </c>
       <c r="E7" s="1">
-        <v>0.5812205042632564</v>
+        <v>0.5812204586440203</v>
       </c>
       <c r="F7" s="1">
-        <v>0.4184787630695445</v>
+        <v>0.4184787302236945</v>
       </c>
       <c r="G7" s="1">
-        <v>0.04795069160171867</v>
+        <v>0.04795068783813169</v>
       </c>
       <c r="H7" s="1">
-        <v>0.1147910495919932</v>
+        <v>0.114791040582194</v>
       </c>
       <c r="I7" s="1">
-        <v>0.4187794957367436</v>
+        <v>0.4187795413559797</v>
       </c>
     </row>
     <row r="8">
@@ -33621,19 +33621,19 @@
         <v>0.1337499999999997</v>
       </c>
       <c r="E2" s="1">
-        <v>0.09187499999999971</v>
+        <v>0.1168749999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0.03750000000000003</v>
+        <v>0.01125</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.08312499999999998</v>
+        <v>0.030625</v>
       </c>
       <c r="J2" s="1">
         <v>0.02625000000000003</v>
@@ -33669,7 +33669,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -33973,25 +33973,25 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.1353920056775413</v>
+        <v>0.1353920017713942</v>
       </c>
       <c r="E7" s="1">
-        <v>0.1220504576728201</v>
+        <v>0.1220504541515853</v>
       </c>
       <c r="F7" s="1">
-        <v>0.02964788445493608</v>
+        <v>0.02964788359957541</v>
       </c>
       <c r="G7" s="1">
-        <v>0.1660281529476417</v>
+        <v>0.1660281481576219</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>0.09536736166337767</v>
+        <v>0.09536735891196749</v>
       </c>
       <c r="J7" s="1">
-        <v>0.02075351911845526</v>
+        <v>0.02075351851970279</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -34000,10 +34000,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0.07115492269184655</v>
+        <v>0.07115492063898092</v>
       </c>
       <c r="N7" s="1">
-        <v>0.04447182668240408</v>
+        <v>0.04447182539936307</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -34015,16 +34015,16 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>0.08499060210415006</v>
+        <v>0.08499059965211612</v>
       </c>
       <c r="S7" s="1">
-        <v>0.02075351911845526</v>
+        <v>0.02075351851970279</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="U7" s="1">
-        <v>0.2093897478683718</v>
+        <v>0.2093897706779899</v>
       </c>
     </row>
     <row r="8">
@@ -38432,7 +38432,7 @@
         </is>
       </c>
       <c r="D2" s="1">
-        <v>0.3974999999999995</v>
+        <v>0.3187499999999995</v>
       </c>
       <c r="E2" s="1">
         <v>0.05625</v>
@@ -38441,7 +38441,7 @@
         <v>0.1787499999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>0.3674999999999997</v>
+        <v>0.4462499999999997</v>
       </c>
     </row>
     <row r="3">
@@ -38577,16 +38577,16 @@
         </is>
       </c>
       <c r="D7" s="1">
-        <v>0.5692393815347722</v>
+        <v>0.5692393651118471</v>
       </c>
       <c r="E7" s="1">
-        <v>0.06522534580085934</v>
+        <v>0.06522534391906586</v>
       </c>
       <c r="F7" s="1">
-        <v>0.1561455247959966</v>
+        <v>0.156145520291097</v>
       </c>
       <c r="G7" s="1">
-        <v>0.2093897478683718</v>
+        <v>0.2093897706779899</v>
       </c>
     </row>
     <row r="8">
